--- a/main_data/evolucion_vinculacion_y_uso_adquirencia_1_a_1.xlsx
+++ b/main_data/evolucion_vinculacion_y_uso_adquirencia_1_a_1.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M52"/>
+  <dimension ref="A1:M54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -497,2194 +497,2280 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>202603</v>
+        <v>202605</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>20260301</t>
+          <t>20260501</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3887</v>
+        <v>3364</v>
       </c>
       <c r="D2" t="n">
-        <v>9756</v>
+        <v>16859</v>
       </c>
       <c r="E2" t="n">
-        <v>191487</v>
+        <v>198590</v>
       </c>
       <c r="F2" t="n">
-        <v>448074</v>
+        <v>448057</v>
       </c>
       <c r="G2" t="n">
-        <v>457831</v>
+        <v>464916</v>
       </c>
       <c r="H2" t="n">
-        <v>4602</v>
+        <v>8447</v>
       </c>
       <c r="I2" t="n">
-        <v>105678</v>
+        <v>108073</v>
       </c>
       <c r="J2" t="n">
-        <v>110281</v>
+        <v>116521</v>
       </c>
       <c r="K2" t="n">
-        <v>0.4717</v>
+        <v>0.501</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2358</v>
+        <v>0.2412</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2409</v>
+        <v>0.2506</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>202602</v>
+        <v>202604</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>20260201</t>
+          <t>20260401</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>3200</v>
+        <v>3739</v>
       </c>
       <c r="D3" t="n">
-        <v>5869</v>
+        <v>13495</v>
       </c>
       <c r="E3" t="n">
-        <v>187600</v>
+        <v>195226</v>
       </c>
       <c r="F3" t="n">
-        <v>448099</v>
+        <v>448056</v>
       </c>
       <c r="G3" t="n">
-        <v>453969</v>
+        <v>461551</v>
       </c>
       <c r="H3" t="n">
-        <v>2617</v>
+        <v>6523</v>
       </c>
       <c r="I3" t="n">
-        <v>103470</v>
+        <v>107059</v>
       </c>
       <c r="J3" t="n">
-        <v>106088</v>
+        <v>113583</v>
       </c>
       <c r="K3" t="n">
-        <v>0.4459</v>
+        <v>0.4834</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2309</v>
+        <v>0.2389</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2337</v>
+        <v>0.2461</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>202601</v>
+        <v>202603</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>20260101</t>
+          <t>20260301</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2669</v>
+        <v>3887</v>
       </c>
       <c r="D4" t="n">
-        <v>2669</v>
+        <v>9756</v>
       </c>
       <c r="E4" t="n">
-        <v>184400</v>
+        <v>191487</v>
       </c>
       <c r="F4" t="n">
-        <v>448103</v>
+        <v>448074</v>
       </c>
       <c r="G4" t="n">
-        <v>450772</v>
+        <v>457831</v>
       </c>
       <c r="H4" t="n">
-        <v>1004</v>
+        <v>4602</v>
       </c>
       <c r="I4" t="n">
-        <v>98960</v>
+        <v>105678</v>
       </c>
       <c r="J4" t="n">
-        <v>99964</v>
+        <v>110281</v>
       </c>
       <c r="K4" t="n">
-        <v>0.3762</v>
+        <v>0.4717</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2208</v>
+        <v>0.2358</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2218</v>
+        <v>0.2409</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>202512</v>
+        <v>202602</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>20251201</t>
+          <t>20260201</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>3412</v>
+        <v>3200</v>
       </c>
       <c r="D5" t="n">
-        <v>38305</v>
+        <v>5869</v>
       </c>
       <c r="E5" t="n">
-        <v>181731</v>
+        <v>187600</v>
       </c>
       <c r="F5" t="n">
-        <v>409803</v>
+        <v>448099</v>
       </c>
       <c r="G5" t="n">
-        <v>448104</v>
+        <v>453969</v>
       </c>
       <c r="H5" t="n">
-        <v>24455</v>
+        <v>2617</v>
       </c>
       <c r="I5" t="n">
-        <v>113080</v>
+        <v>103470</v>
       </c>
       <c r="J5" t="n">
-        <v>137535</v>
+        <v>106088</v>
       </c>
       <c r="K5" t="n">
-        <v>0.6384</v>
+        <v>0.4459</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2759</v>
+        <v>0.2309</v>
       </c>
       <c r="M5" t="n">
-        <v>0.3069</v>
+        <v>0.2337</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>202511</v>
+        <v>202601</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>20251101</t>
+          <t>20260101</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>3284</v>
+        <v>2669</v>
       </c>
       <c r="D6" t="n">
-        <v>34893</v>
+        <v>2669</v>
       </c>
       <c r="E6" t="n">
-        <v>178319</v>
+        <v>184400</v>
       </c>
       <c r="F6" t="n">
-        <v>409832</v>
+        <v>448103</v>
       </c>
       <c r="G6" t="n">
-        <v>444725</v>
+        <v>450772</v>
       </c>
       <c r="H6" t="n">
-        <v>22119</v>
+        <v>1004</v>
       </c>
       <c r="I6" t="n">
-        <v>112697</v>
+        <v>98960</v>
       </c>
       <c r="J6" t="n">
-        <v>134816</v>
+        <v>99964</v>
       </c>
       <c r="K6" t="n">
-        <v>0.6339</v>
+        <v>0.3762</v>
       </c>
       <c r="L6" t="n">
-        <v>0.275</v>
+        <v>0.2208</v>
       </c>
       <c r="M6" t="n">
-        <v>0.3031</v>
+        <v>0.2218</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>202510</v>
+        <v>202512</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>20251001</t>
+          <t>20251201</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3759</v>
+        <v>3412</v>
       </c>
       <c r="D7" t="n">
-        <v>31609</v>
+        <v>38305</v>
       </c>
       <c r="E7" t="n">
-        <v>175035</v>
+        <v>181731</v>
       </c>
       <c r="F7" t="n">
-        <v>409896</v>
+        <v>409803</v>
       </c>
       <c r="G7" t="n">
-        <v>441505</v>
+        <v>448104</v>
       </c>
       <c r="H7" t="n">
-        <v>20079</v>
+        <v>24455</v>
       </c>
       <c r="I7" t="n">
-        <v>112384</v>
+        <v>113080</v>
       </c>
       <c r="J7" t="n">
-        <v>132463</v>
+        <v>137535</v>
       </c>
       <c r="K7" t="n">
-        <v>0.6352</v>
+        <v>0.6384</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2742</v>
+        <v>0.2759</v>
       </c>
       <c r="M7" t="n">
-        <v>0.3</v>
+        <v>0.3069</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>202509</v>
+        <v>202511</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>20250901</t>
+          <t>20251101</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>3640</v>
+        <v>3284</v>
       </c>
       <c r="D8" t="n">
-        <v>27850</v>
+        <v>34893</v>
       </c>
       <c r="E8" t="n">
-        <v>171276</v>
+        <v>178319</v>
       </c>
       <c r="F8" t="n">
-        <v>409900</v>
+        <v>409832</v>
       </c>
       <c r="G8" t="n">
-        <v>437750</v>
+        <v>444725</v>
       </c>
       <c r="H8" t="n">
-        <v>17741</v>
+        <v>22119</v>
       </c>
       <c r="I8" t="n">
-        <v>111995</v>
+        <v>112697</v>
       </c>
       <c r="J8" t="n">
-        <v>129736</v>
+        <v>134816</v>
       </c>
       <c r="K8" t="n">
-        <v>0.637</v>
+        <v>0.6339</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2732</v>
+        <v>0.275</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2964</v>
+        <v>0.3031</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>202508</v>
+        <v>202510</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>20250801</t>
+          <t>20251001</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2970</v>
+        <v>3759</v>
       </c>
       <c r="D9" t="n">
-        <v>24210</v>
+        <v>31609</v>
       </c>
       <c r="E9" t="n">
-        <v>167636</v>
+        <v>175035</v>
       </c>
       <c r="F9" t="n">
-        <v>409903</v>
+        <v>409896</v>
       </c>
       <c r="G9" t="n">
-        <v>434113</v>
+        <v>441505</v>
       </c>
       <c r="H9" t="n">
-        <v>15543</v>
+        <v>20079</v>
       </c>
       <c r="I9" t="n">
-        <v>111498</v>
+        <v>112384</v>
       </c>
       <c r="J9" t="n">
-        <v>127041</v>
+        <v>132463</v>
       </c>
       <c r="K9" t="n">
-        <v>0.642</v>
+        <v>0.6352</v>
       </c>
       <c r="L9" t="n">
-        <v>0.272</v>
+        <v>0.2742</v>
       </c>
       <c r="M9" t="n">
-        <v>0.2926</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>202507</v>
+        <v>202509</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>20250701</t>
+          <t>20250901</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>3699</v>
+        <v>3640</v>
       </c>
       <c r="D10" t="n">
-        <v>21240</v>
+        <v>27850</v>
       </c>
       <c r="E10" t="n">
-        <v>164666</v>
+        <v>171276</v>
       </c>
       <c r="F10" t="n">
-        <v>409905</v>
+        <v>409900</v>
       </c>
       <c r="G10" t="n">
-        <v>431145</v>
+        <v>437750</v>
       </c>
       <c r="H10" t="n">
-        <v>13549</v>
+        <v>17741</v>
       </c>
       <c r="I10" t="n">
-        <v>110935</v>
+        <v>111995</v>
       </c>
       <c r="J10" t="n">
-        <v>124484</v>
+        <v>129736</v>
       </c>
       <c r="K10" t="n">
-        <v>0.6379</v>
+        <v>0.637</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2706</v>
+        <v>0.2732</v>
       </c>
       <c r="M10" t="n">
-        <v>0.2887</v>
+        <v>0.2964</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>202506</v>
+        <v>202508</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>20250601</t>
+          <t>20250801</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>3151</v>
+        <v>2970</v>
       </c>
       <c r="D11" t="n">
-        <v>17541</v>
+        <v>24210</v>
       </c>
       <c r="E11" t="n">
-        <v>160967</v>
+        <v>167636</v>
       </c>
       <c r="F11" t="n">
-        <v>409922</v>
+        <v>409903</v>
       </c>
       <c r="G11" t="n">
-        <v>427463</v>
+        <v>434113</v>
       </c>
       <c r="H11" t="n">
-        <v>11155</v>
+        <v>15543</v>
       </c>
       <c r="I11" t="n">
-        <v>110174</v>
+        <v>111498</v>
       </c>
       <c r="J11" t="n">
-        <v>121329</v>
+        <v>127041</v>
       </c>
       <c r="K11" t="n">
-        <v>0.6359</v>
+        <v>0.642</v>
       </c>
       <c r="L11" t="n">
-        <v>0.2688</v>
+        <v>0.272</v>
       </c>
       <c r="M11" t="n">
-        <v>0.2838</v>
+        <v>0.2926</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>202505</v>
+        <v>202507</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>20250501</t>
+          <t>20250701</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>3231</v>
+        <v>3699</v>
       </c>
       <c r="D12" t="n">
-        <v>14390</v>
+        <v>21240</v>
       </c>
       <c r="E12" t="n">
-        <v>157816</v>
+        <v>164666</v>
       </c>
       <c r="F12" t="n">
-        <v>409925</v>
+        <v>409905</v>
       </c>
       <c r="G12" t="n">
-        <v>424315</v>
+        <v>431145</v>
       </c>
       <c r="H12" t="n">
-        <v>9084</v>
+        <v>13549</v>
       </c>
       <c r="I12" t="n">
-        <v>109362</v>
+        <v>110935</v>
       </c>
       <c r="J12" t="n">
-        <v>118446</v>
+        <v>124484</v>
       </c>
       <c r="K12" t="n">
-        <v>0.6313</v>
+        <v>0.6379</v>
       </c>
       <c r="L12" t="n">
-        <v>0.2668</v>
+        <v>0.2706</v>
       </c>
       <c r="M12" t="n">
-        <v>0.2791</v>
+        <v>0.2887</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>202504</v>
+        <v>202506</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>20250401</t>
+          <t>20250601</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>3317</v>
+        <v>3151</v>
       </c>
       <c r="D13" t="n">
-        <v>11159</v>
+        <v>17541</v>
       </c>
       <c r="E13" t="n">
-        <v>154585</v>
+        <v>160967</v>
       </c>
       <c r="F13" t="n">
-        <v>409928</v>
+        <v>409922</v>
       </c>
       <c r="G13" t="n">
-        <v>421087</v>
+        <v>427463</v>
       </c>
       <c r="H13" t="n">
-        <v>6861</v>
+        <v>11155</v>
       </c>
       <c r="I13" t="n">
-        <v>108111</v>
+        <v>110174</v>
       </c>
       <c r="J13" t="n">
-        <v>114972</v>
+        <v>121329</v>
       </c>
       <c r="K13" t="n">
-        <v>0.6148</v>
+        <v>0.6359</v>
       </c>
       <c r="L13" t="n">
-        <v>0.2637</v>
+        <v>0.2688</v>
       </c>
       <c r="M13" t="n">
-        <v>0.273</v>
+        <v>0.2838</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>202503</v>
+        <v>202505</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>20250301</t>
+          <t>20250501</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2887</v>
+        <v>3231</v>
       </c>
       <c r="D14" t="n">
-        <v>7842</v>
+        <v>14390</v>
       </c>
       <c r="E14" t="n">
-        <v>151268</v>
+        <v>157816</v>
       </c>
       <c r="F14" t="n">
-        <v>409953</v>
+        <v>409925</v>
       </c>
       <c r="G14" t="n">
-        <v>417795</v>
+        <v>424315</v>
       </c>
       <c r="H14" t="n">
-        <v>4674</v>
+        <v>9084</v>
       </c>
       <c r="I14" t="n">
-        <v>106615</v>
+        <v>109362</v>
       </c>
       <c r="J14" t="n">
-        <v>111289</v>
+        <v>118446</v>
       </c>
       <c r="K14" t="n">
-        <v>0.596</v>
+        <v>0.6313</v>
       </c>
       <c r="L14" t="n">
-        <v>0.2601</v>
+        <v>0.2668</v>
       </c>
       <c r="M14" t="n">
-        <v>0.2664</v>
+        <v>0.2791</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>202502</v>
+        <v>202504</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>20250201</t>
+          <t>20250401</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2691</v>
+        <v>3317</v>
       </c>
       <c r="D15" t="n">
-        <v>4955</v>
+        <v>11159</v>
       </c>
       <c r="E15" t="n">
-        <v>148381</v>
+        <v>154585</v>
       </c>
       <c r="F15" t="n">
-        <v>409938</v>
+        <v>409928</v>
       </c>
       <c r="G15" t="n">
-        <v>414893</v>
+        <v>421087</v>
       </c>
       <c r="H15" t="n">
-        <v>2828</v>
+        <v>6861</v>
       </c>
       <c r="I15" t="n">
-        <v>104133</v>
+        <v>108111</v>
       </c>
       <c r="J15" t="n">
-        <v>106961</v>
+        <v>114972</v>
       </c>
       <c r="K15" t="n">
-        <v>0.5707</v>
+        <v>0.6148</v>
       </c>
       <c r="L15" t="n">
-        <v>0.254</v>
+        <v>0.2637</v>
       </c>
       <c r="M15" t="n">
-        <v>0.2578</v>
+        <v>0.273</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>202501</v>
+        <v>202503</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>20250101</t>
+          <t>20250301</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>2264</v>
+        <v>2887</v>
       </c>
       <c r="D16" t="n">
-        <v>2264</v>
+        <v>7842</v>
       </c>
       <c r="E16" t="n">
-        <v>145690</v>
+        <v>151268</v>
       </c>
       <c r="F16" t="n">
-        <v>410060</v>
+        <v>409953</v>
       </c>
       <c r="G16" t="n">
-        <v>412324</v>
+        <v>417795</v>
       </c>
       <c r="H16" t="n">
-        <v>1159</v>
+        <v>4674</v>
       </c>
       <c r="I16" t="n">
-        <v>99434</v>
+        <v>106615</v>
       </c>
       <c r="J16" t="n">
-        <v>100593</v>
+        <v>111289</v>
       </c>
       <c r="K16" t="n">
-        <v>0.5119</v>
+        <v>0.596</v>
       </c>
       <c r="L16" t="n">
-        <v>0.2425</v>
+        <v>0.2601</v>
       </c>
       <c r="M16" t="n">
-        <v>0.244</v>
+        <v>0.2664</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>202412</v>
+        <v>202502</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>20241201</t>
+          <t>20250201</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>2910</v>
+        <v>2691</v>
       </c>
       <c r="D17" t="n">
-        <v>38529</v>
+        <v>4955</v>
       </c>
       <c r="E17" t="n">
-        <v>143426</v>
+        <v>148381</v>
       </c>
       <c r="F17" t="n">
-        <v>371557</v>
+        <v>409938</v>
       </c>
       <c r="G17" t="n">
-        <v>410078</v>
+        <v>414893</v>
       </c>
       <c r="H17" t="n">
-        <v>28109</v>
+        <v>2828</v>
       </c>
       <c r="I17" t="n">
-        <v>122366</v>
+        <v>104133</v>
       </c>
       <c r="J17" t="n">
-        <v>150475</v>
+        <v>106961</v>
       </c>
       <c r="K17" t="n">
-        <v>0.7296</v>
+        <v>0.5707</v>
       </c>
       <c r="L17" t="n">
-        <v>0.3293</v>
+        <v>0.254</v>
       </c>
       <c r="M17" t="n">
-        <v>0.3669</v>
+        <v>0.2578</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>202411</v>
+        <v>202501</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>20241101</t>
+          <t>20250101</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>2980</v>
+        <v>2264</v>
       </c>
       <c r="D18" t="n">
-        <v>35619</v>
+        <v>2264</v>
       </c>
       <c r="E18" t="n">
-        <v>140516</v>
+        <v>145690</v>
       </c>
       <c r="F18" t="n">
-        <v>371563</v>
+        <v>410060</v>
       </c>
       <c r="G18" t="n">
-        <v>407176</v>
+        <v>412324</v>
       </c>
       <c r="H18" t="n">
-        <v>25789</v>
+        <v>1159</v>
       </c>
       <c r="I18" t="n">
-        <v>122024</v>
+        <v>99434</v>
       </c>
       <c r="J18" t="n">
-        <v>147813</v>
+        <v>100593</v>
       </c>
       <c r="K18" t="n">
-        <v>0.724</v>
+        <v>0.5119</v>
       </c>
       <c r="L18" t="n">
-        <v>0.3284</v>
+        <v>0.2425</v>
       </c>
       <c r="M18" t="n">
-        <v>0.363</v>
+        <v>0.244</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>202410</v>
+        <v>202412</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>20241001</t>
+          <t>20241201</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>3113</v>
+        <v>2910</v>
       </c>
       <c r="D19" t="n">
-        <v>32639</v>
+        <v>38529</v>
       </c>
       <c r="E19" t="n">
-        <v>137536</v>
+        <v>143426</v>
       </c>
       <c r="F19" t="n">
-        <v>371563</v>
+        <v>371557</v>
       </c>
       <c r="G19" t="n">
-        <v>404196</v>
+        <v>410078</v>
       </c>
       <c r="H19" t="n">
-        <v>23547</v>
+        <v>28109</v>
       </c>
       <c r="I19" t="n">
-        <v>121582</v>
+        <v>122366</v>
       </c>
       <c r="J19" t="n">
-        <v>145129</v>
+        <v>150475</v>
       </c>
       <c r="K19" t="n">
-        <v>0.7214</v>
+        <v>0.7296</v>
       </c>
       <c r="L19" t="n">
-        <v>0.3272</v>
+        <v>0.3293</v>
       </c>
       <c r="M19" t="n">
-        <v>0.3591</v>
+        <v>0.3669</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>202409</v>
+        <v>202411</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>20240901</t>
+          <t>20241101</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>3706</v>
+        <v>2980</v>
       </c>
       <c r="D20" t="n">
-        <v>29526</v>
+        <v>35619</v>
       </c>
       <c r="E20" t="n">
-        <v>134423</v>
+        <v>140516</v>
       </c>
       <c r="F20" t="n">
-        <v>371574</v>
+        <v>371563</v>
       </c>
       <c r="G20" t="n">
-        <v>401097</v>
+        <v>407176</v>
       </c>
       <c r="H20" t="n">
-        <v>21278</v>
+        <v>25789</v>
       </c>
       <c r="I20" t="n">
-        <v>121138</v>
+        <v>122024</v>
       </c>
       <c r="J20" t="n">
-        <v>142416</v>
+        <v>147813</v>
       </c>
       <c r="K20" t="n">
-        <v>0.7207</v>
+        <v>0.724</v>
       </c>
       <c r="L20" t="n">
-        <v>0.326</v>
+        <v>0.3284</v>
       </c>
       <c r="M20" t="n">
-        <v>0.3551</v>
+        <v>0.363</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>202408</v>
+        <v>202410</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>20240801</t>
+          <t>20241001</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>3077</v>
+        <v>3113</v>
       </c>
       <c r="D21" t="n">
-        <v>25820</v>
+        <v>32639</v>
       </c>
       <c r="E21" t="n">
-        <v>130717</v>
+        <v>137536</v>
       </c>
       <c r="F21" t="n">
-        <v>371579</v>
+        <v>371563</v>
       </c>
       <c r="G21" t="n">
-        <v>397396</v>
+        <v>404196</v>
       </c>
       <c r="H21" t="n">
-        <v>18489</v>
+        <v>23547</v>
       </c>
       <c r="I21" t="n">
-        <v>120662</v>
+        <v>121582</v>
       </c>
       <c r="J21" t="n">
-        <v>139151</v>
+        <v>145129</v>
       </c>
       <c r="K21" t="n">
-        <v>0.7161</v>
+        <v>0.7214</v>
       </c>
       <c r="L21" t="n">
-        <v>0.3247</v>
+        <v>0.3272</v>
       </c>
       <c r="M21" t="n">
-        <v>0.3502</v>
+        <v>0.3591</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>202407</v>
+        <v>202409</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>20240701</t>
+          <t>20240901</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>3250</v>
+        <v>3706</v>
       </c>
       <c r="D22" t="n">
-        <v>22743</v>
+        <v>29526</v>
       </c>
       <c r="E22" t="n">
-        <v>127640</v>
+        <v>134423</v>
       </c>
       <c r="F22" t="n">
-        <v>371589</v>
+        <v>371574</v>
       </c>
       <c r="G22" t="n">
-        <v>394329</v>
+        <v>401097</v>
       </c>
       <c r="H22" t="n">
-        <v>16281</v>
+        <v>21278</v>
       </c>
       <c r="I22" t="n">
-        <v>120039</v>
+        <v>121138</v>
       </c>
       <c r="J22" t="n">
-        <v>136320</v>
+        <v>142416</v>
       </c>
       <c r="K22" t="n">
-        <v>0.7159</v>
+        <v>0.7207</v>
       </c>
       <c r="L22" t="n">
-        <v>0.323</v>
+        <v>0.326</v>
       </c>
       <c r="M22" t="n">
-        <v>0.3457</v>
+        <v>0.3551</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>202406</v>
+        <v>202408</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>20240601</t>
+          <t>20240801</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>2683</v>
+        <v>3077</v>
       </c>
       <c r="D23" t="n">
-        <v>19493</v>
+        <v>25820</v>
       </c>
       <c r="E23" t="n">
-        <v>124390</v>
+        <v>130717</v>
       </c>
       <c r="F23" t="n">
-        <v>371581</v>
+        <v>371579</v>
       </c>
       <c r="G23" t="n">
-        <v>391072</v>
+        <v>397396</v>
       </c>
       <c r="H23" t="n">
-        <v>14112</v>
+        <v>18489</v>
       </c>
       <c r="I23" t="n">
-        <v>119205</v>
+        <v>120662</v>
       </c>
       <c r="J23" t="n">
-        <v>133317</v>
+        <v>139151</v>
       </c>
       <c r="K23" t="n">
-        <v>0.724</v>
+        <v>0.7161</v>
       </c>
       <c r="L23" t="n">
-        <v>0.3208</v>
+        <v>0.3247</v>
       </c>
       <c r="M23" t="n">
-        <v>0.3409</v>
+        <v>0.3502</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>202405</v>
+        <v>202407</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>20240501</t>
+          <t>20240701</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>2946</v>
+        <v>3250</v>
       </c>
       <c r="D24" t="n">
-        <v>16810</v>
+        <v>22743</v>
       </c>
       <c r="E24" t="n">
-        <v>121707</v>
+        <v>127640</v>
       </c>
       <c r="F24" t="n">
-        <v>371587</v>
+        <v>371589</v>
       </c>
       <c r="G24" t="n">
-        <v>388397</v>
+        <v>394329</v>
       </c>
       <c r="H24" t="n">
-        <v>12260</v>
+        <v>16281</v>
       </c>
       <c r="I24" t="n">
-        <v>118299</v>
+        <v>120039</v>
       </c>
       <c r="J24" t="n">
-        <v>130559</v>
+        <v>136320</v>
       </c>
       <c r="K24" t="n">
-        <v>0.7292999999999999</v>
+        <v>0.7159</v>
       </c>
       <c r="L24" t="n">
-        <v>0.3184</v>
+        <v>0.323</v>
       </c>
       <c r="M24" t="n">
-        <v>0.3361</v>
+        <v>0.3457</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>202404</v>
+        <v>202406</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>20240401</t>
+          <t>20240601</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>3198</v>
+        <v>2683</v>
       </c>
       <c r="D25" t="n">
-        <v>13864</v>
+        <v>19493</v>
       </c>
       <c r="E25" t="n">
-        <v>118761</v>
+        <v>124390</v>
       </c>
       <c r="F25" t="n">
-        <v>371594</v>
+        <v>371581</v>
       </c>
       <c r="G25" t="n">
-        <v>385458</v>
+        <v>391072</v>
       </c>
       <c r="H25" t="n">
-        <v>9995</v>
+        <v>14112</v>
       </c>
       <c r="I25" t="n">
-        <v>116888</v>
+        <v>119205</v>
       </c>
       <c r="J25" t="n">
-        <v>126883</v>
+        <v>133317</v>
       </c>
       <c r="K25" t="n">
-        <v>0.7209</v>
+        <v>0.724</v>
       </c>
       <c r="L25" t="n">
-        <v>0.3146</v>
+        <v>0.3208</v>
       </c>
       <c r="M25" t="n">
-        <v>0.3292</v>
+        <v>0.3409</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>202403</v>
+        <v>202405</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>20240301</t>
+          <t>20240501</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>3430</v>
+        <v>2946</v>
       </c>
       <c r="D26" t="n">
-        <v>10666</v>
+        <v>16810</v>
       </c>
       <c r="E26" t="n">
-        <v>115563</v>
+        <v>121707</v>
       </c>
       <c r="F26" t="n">
-        <v>371607</v>
+        <v>371587</v>
       </c>
       <c r="G26" t="n">
-        <v>382273</v>
+        <v>388397</v>
       </c>
       <c r="H26" t="n">
-        <v>7763</v>
+        <v>12260</v>
       </c>
       <c r="I26" t="n">
-        <v>115020</v>
+        <v>118299</v>
       </c>
       <c r="J26" t="n">
-        <v>122783</v>
+        <v>130559</v>
       </c>
       <c r="K26" t="n">
-        <v>0.7278</v>
+        <v>0.7292999999999999</v>
       </c>
       <c r="L26" t="n">
-        <v>0.3095</v>
+        <v>0.3184</v>
       </c>
       <c r="M26" t="n">
-        <v>0.3212</v>
+        <v>0.3361</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>202402</v>
+        <v>202404</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>20240201</t>
+          <t>20240401</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>4092</v>
+        <v>3198</v>
       </c>
       <c r="D27" t="n">
-        <v>7236</v>
+        <v>13864</v>
       </c>
       <c r="E27" t="n">
-        <v>112133</v>
+        <v>118761</v>
       </c>
       <c r="F27" t="n">
-        <v>371597</v>
+        <v>371594</v>
       </c>
       <c r="G27" t="n">
-        <v>378833</v>
+        <v>385458</v>
       </c>
       <c r="H27" t="n">
-        <v>4888</v>
+        <v>9995</v>
       </c>
       <c r="I27" t="n">
-        <v>112247</v>
+        <v>116888</v>
       </c>
       <c r="J27" t="n">
-        <v>117135</v>
+        <v>126883</v>
       </c>
       <c r="K27" t="n">
-        <v>0.6755</v>
+        <v>0.7209</v>
       </c>
       <c r="L27" t="n">
-        <v>0.3021</v>
+        <v>0.3146</v>
       </c>
       <c r="M27" t="n">
-        <v>0.3092</v>
+        <v>0.3292</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>202401</v>
+        <v>202403</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>20240101</t>
+          <t>20240301</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>3144</v>
+        <v>3430</v>
       </c>
       <c r="D28" t="n">
-        <v>3144</v>
+        <v>10666</v>
       </c>
       <c r="E28" t="n">
-        <v>108041</v>
+        <v>115563</v>
       </c>
       <c r="F28" t="n">
-        <v>372060</v>
+        <v>371607</v>
       </c>
       <c r="G28" t="n">
-        <v>375204</v>
+        <v>382273</v>
       </c>
       <c r="H28" t="n">
-        <v>1985</v>
+        <v>7763</v>
       </c>
       <c r="I28" t="n">
-        <v>106338</v>
+        <v>115020</v>
       </c>
       <c r="J28" t="n">
-        <v>108323</v>
+        <v>122783</v>
       </c>
       <c r="K28" t="n">
-        <v>0.6314</v>
+        <v>0.7278</v>
       </c>
       <c r="L28" t="n">
-        <v>0.2858</v>
+        <v>0.3095</v>
       </c>
       <c r="M28" t="n">
-        <v>0.2887</v>
+        <v>0.3212</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>202312</v>
+        <v>202402</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>20231201</t>
+          <t>20240201</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>3689</v>
+        <v>4092</v>
       </c>
       <c r="D29" t="n">
-        <v>53417</v>
+        <v>7236</v>
       </c>
       <c r="E29" t="n">
-        <v>104897</v>
+        <v>112133</v>
       </c>
       <c r="F29" t="n">
-        <v>318660</v>
+        <v>371597</v>
       </c>
       <c r="G29" t="n">
-        <v>372067</v>
+        <v>378833</v>
       </c>
       <c r="H29" t="n">
-        <v>39969</v>
+        <v>4888</v>
       </c>
       <c r="I29" t="n">
-        <v>121536</v>
+        <v>112247</v>
       </c>
       <c r="J29" t="n">
-        <v>161505</v>
+        <v>117135</v>
       </c>
       <c r="K29" t="n">
-        <v>0.7482</v>
+        <v>0.6755</v>
       </c>
       <c r="L29" t="n">
-        <v>0.3814</v>
+        <v>0.3021</v>
       </c>
       <c r="M29" t="n">
-        <v>0.4341</v>
+        <v>0.3092</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>202311</v>
+        <v>202401</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>20231101</t>
+          <t>20240101</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>5106</v>
+        <v>3144</v>
       </c>
       <c r="D30" t="n">
-        <v>49728</v>
+        <v>3144</v>
       </c>
       <c r="E30" t="n">
-        <v>101208</v>
+        <v>108041</v>
       </c>
       <c r="F30" t="n">
-        <v>318662</v>
+        <v>372060</v>
       </c>
       <c r="G30" t="n">
-        <v>368382</v>
+        <v>375204</v>
       </c>
       <c r="H30" t="n">
-        <v>36374</v>
+        <v>1985</v>
       </c>
       <c r="I30" t="n">
-        <v>121172</v>
+        <v>106338</v>
       </c>
       <c r="J30" t="n">
-        <v>157546</v>
+        <v>108323</v>
       </c>
       <c r="K30" t="n">
-        <v>0.7315</v>
+        <v>0.6314</v>
       </c>
       <c r="L30" t="n">
-        <v>0.3803</v>
+        <v>0.2858</v>
       </c>
       <c r="M30" t="n">
-        <v>0.4277</v>
+        <v>0.2887</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>202310</v>
+        <v>202312</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>20231001</t>
+          <t>20231201</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>4645</v>
+        <v>3689</v>
       </c>
       <c r="D31" t="n">
-        <v>44622</v>
+        <v>53417</v>
       </c>
       <c r="E31" t="n">
-        <v>96102</v>
+        <v>104897</v>
       </c>
       <c r="F31" t="n">
-        <v>318666</v>
+        <v>318660</v>
       </c>
       <c r="G31" t="n">
-        <v>363280</v>
+        <v>372067</v>
       </c>
       <c r="H31" t="n">
-        <v>32585</v>
+        <v>39969</v>
       </c>
       <c r="I31" t="n">
-        <v>120746</v>
+        <v>121536</v>
       </c>
       <c r="J31" t="n">
-        <v>153331</v>
+        <v>161505</v>
       </c>
       <c r="K31" t="n">
-        <v>0.7302</v>
+        <v>0.7482</v>
       </c>
       <c r="L31" t="n">
-        <v>0.3789</v>
+        <v>0.3814</v>
       </c>
       <c r="M31" t="n">
-        <v>0.4221</v>
+        <v>0.4341</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>202309</v>
+        <v>202311</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>20230901</t>
+          <t>20231101</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>4565</v>
+        <v>5106</v>
       </c>
       <c r="D32" t="n">
-        <v>39977</v>
+        <v>49728</v>
       </c>
       <c r="E32" t="n">
-        <v>91457</v>
+        <v>101208</v>
       </c>
       <c r="F32" t="n">
-        <v>318668</v>
+        <v>318662</v>
       </c>
       <c r="G32" t="n">
-        <v>358637</v>
+        <v>368382</v>
       </c>
       <c r="H32" t="n">
-        <v>29174</v>
+        <v>36374</v>
       </c>
       <c r="I32" t="n">
-        <v>120319</v>
+        <v>121172</v>
       </c>
       <c r="J32" t="n">
-        <v>149493</v>
+        <v>157546</v>
       </c>
       <c r="K32" t="n">
-        <v>0.7298</v>
+        <v>0.7315</v>
       </c>
       <c r="L32" t="n">
-        <v>0.3776</v>
+        <v>0.3803</v>
       </c>
       <c r="M32" t="n">
-        <v>0.4168</v>
+        <v>0.4277</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>202308</v>
+        <v>202310</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>20230801</t>
+          <t>20231001</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>4453</v>
+        <v>4645</v>
       </c>
       <c r="D33" t="n">
-        <v>35412</v>
+        <v>44622</v>
       </c>
       <c r="E33" t="n">
-        <v>86892</v>
+        <v>96102</v>
       </c>
       <c r="F33" t="n">
-        <v>318670</v>
+        <v>318666</v>
       </c>
       <c r="G33" t="n">
-        <v>354074</v>
+        <v>363280</v>
       </c>
       <c r="H33" t="n">
-        <v>25578</v>
+        <v>32585</v>
       </c>
       <c r="I33" t="n">
-        <v>119743</v>
+        <v>120746</v>
       </c>
       <c r="J33" t="n">
-        <v>145321</v>
+        <v>153331</v>
       </c>
       <c r="K33" t="n">
-        <v>0.7223000000000001</v>
+        <v>0.7302</v>
       </c>
       <c r="L33" t="n">
-        <v>0.3758</v>
+        <v>0.3789</v>
       </c>
       <c r="M33" t="n">
-        <v>0.4104</v>
+        <v>0.4221</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>202307</v>
+        <v>202309</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>20230701</t>
+          <t>20230901</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>4990</v>
+        <v>4565</v>
       </c>
       <c r="D34" t="n">
-        <v>30959</v>
+        <v>39977</v>
       </c>
       <c r="E34" t="n">
-        <v>82439</v>
+        <v>91457</v>
       </c>
       <c r="F34" t="n">
-        <v>318670</v>
+        <v>318668</v>
       </c>
       <c r="G34" t="n">
-        <v>349621</v>
+        <v>358637</v>
       </c>
       <c r="H34" t="n">
-        <v>21917</v>
+        <v>29174</v>
       </c>
       <c r="I34" t="n">
-        <v>118972</v>
+        <v>120319</v>
       </c>
       <c r="J34" t="n">
-        <v>140889</v>
+        <v>149493</v>
       </c>
       <c r="K34" t="n">
-        <v>0.7079</v>
+        <v>0.7298</v>
       </c>
       <c r="L34" t="n">
-        <v>0.3733</v>
+        <v>0.3776</v>
       </c>
       <c r="M34" t="n">
-        <v>0.403</v>
+        <v>0.4168</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>202306</v>
+        <v>202308</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>20230601</t>
+          <t>20230801</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>4676</v>
+        <v>4453</v>
       </c>
       <c r="D35" t="n">
-        <v>25969</v>
+        <v>35412</v>
       </c>
       <c r="E35" t="n">
-        <v>77449</v>
+        <v>86892</v>
       </c>
       <c r="F35" t="n">
-        <v>318673</v>
+        <v>318670</v>
       </c>
       <c r="G35" t="n">
-        <v>344634</v>
+        <v>354074</v>
       </c>
       <c r="H35" t="n">
-        <v>18330</v>
+        <v>25578</v>
       </c>
       <c r="I35" t="n">
-        <v>118009</v>
+        <v>119743</v>
       </c>
       <c r="J35" t="n">
-        <v>136339</v>
+        <v>145321</v>
       </c>
       <c r="K35" t="n">
-        <v>0.7058</v>
+        <v>0.7223000000000001</v>
       </c>
       <c r="L35" t="n">
-        <v>0.3703</v>
+        <v>0.3758</v>
       </c>
       <c r="M35" t="n">
-        <v>0.3956</v>
+        <v>0.4104</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>202305</v>
+        <v>202307</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>20230501</t>
+          <t>20230701</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>5112</v>
+        <v>4990</v>
       </c>
       <c r="D36" t="n">
-        <v>21293</v>
+        <v>30959</v>
       </c>
       <c r="E36" t="n">
-        <v>72773</v>
+        <v>82439</v>
       </c>
       <c r="F36" t="n">
-        <v>318680</v>
+        <v>318670</v>
       </c>
       <c r="G36" t="n">
-        <v>339967</v>
+        <v>349621</v>
       </c>
       <c r="H36" t="n">
-        <v>14716</v>
+        <v>21917</v>
       </c>
       <c r="I36" t="n">
-        <v>116996</v>
+        <v>118972</v>
       </c>
       <c r="J36" t="n">
-        <v>131712</v>
+        <v>140889</v>
       </c>
       <c r="K36" t="n">
-        <v>0.6911</v>
+        <v>0.7079</v>
       </c>
       <c r="L36" t="n">
-        <v>0.3671</v>
+        <v>0.3733</v>
       </c>
       <c r="M36" t="n">
-        <v>0.3874</v>
+        <v>0.403</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>202304</v>
+        <v>202306</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>20230401</t>
+          <t>20230601</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>4006</v>
+        <v>4676</v>
       </c>
       <c r="D37" t="n">
-        <v>16181</v>
+        <v>25969</v>
       </c>
       <c r="E37" t="n">
-        <v>67661</v>
+        <v>77449</v>
       </c>
       <c r="F37" t="n">
-        <v>318953</v>
+        <v>318673</v>
       </c>
       <c r="G37" t="n">
-        <v>335134</v>
+        <v>344634</v>
       </c>
       <c r="H37" t="n">
-        <v>11281</v>
+        <v>18330</v>
       </c>
       <c r="I37" t="n">
-        <v>115676</v>
+        <v>118009</v>
       </c>
       <c r="J37" t="n">
-        <v>126957</v>
+        <v>136339</v>
       </c>
       <c r="K37" t="n">
-        <v>0.6972</v>
+        <v>0.7058</v>
       </c>
       <c r="L37" t="n">
-        <v>0.3627</v>
+        <v>0.3703</v>
       </c>
       <c r="M37" t="n">
-        <v>0.3788</v>
+        <v>0.3956</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>202303</v>
+        <v>202305</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>20230301</t>
+          <t>20230501</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>4810</v>
+        <v>5112</v>
       </c>
       <c r="D38" t="n">
-        <v>12175</v>
+        <v>21293</v>
       </c>
       <c r="E38" t="n">
-        <v>63655</v>
+        <v>72773</v>
       </c>
       <c r="F38" t="n">
-        <v>318956</v>
+        <v>318680</v>
       </c>
       <c r="G38" t="n">
-        <v>331131</v>
+        <v>339967</v>
       </c>
       <c r="H38" t="n">
-        <v>8370</v>
+        <v>14716</v>
       </c>
       <c r="I38" t="n">
-        <v>113892</v>
+        <v>116996</v>
       </c>
       <c r="J38" t="n">
-        <v>122262</v>
+        <v>131712</v>
       </c>
       <c r="K38" t="n">
-        <v>0.6875</v>
+        <v>0.6911</v>
       </c>
       <c r="L38" t="n">
-        <v>0.3571</v>
+        <v>0.3671</v>
       </c>
       <c r="M38" t="n">
-        <v>0.3692</v>
+        <v>0.3874</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>202302</v>
+        <v>202304</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>20230201</t>
+          <t>20230401</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>3874</v>
+        <v>4006</v>
       </c>
       <c r="D39" t="n">
-        <v>7365</v>
+        <v>16181</v>
       </c>
       <c r="E39" t="n">
-        <v>58845</v>
+        <v>67661</v>
       </c>
       <c r="F39" t="n">
-        <v>318971</v>
+        <v>318953</v>
       </c>
       <c r="G39" t="n">
-        <v>326336</v>
+        <v>335134</v>
       </c>
       <c r="H39" t="n">
-        <v>4945</v>
+        <v>11281</v>
       </c>
       <c r="I39" t="n">
-        <v>110993</v>
+        <v>115676</v>
       </c>
       <c r="J39" t="n">
-        <v>115938</v>
+        <v>126957</v>
       </c>
       <c r="K39" t="n">
-        <v>0.6714</v>
+        <v>0.6972</v>
       </c>
       <c r="L39" t="n">
-        <v>0.348</v>
+        <v>0.3627</v>
       </c>
       <c r="M39" t="n">
-        <v>0.3553</v>
+        <v>0.3788</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>202301</v>
+        <v>202303</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>20230101</t>
+          <t>20230301</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>3491</v>
+        <v>4810</v>
       </c>
       <c r="D40" t="n">
-        <v>3491</v>
+        <v>12175</v>
       </c>
       <c r="E40" t="n">
-        <v>54971</v>
+        <v>63655</v>
       </c>
       <c r="F40" t="n">
-        <v>318972</v>
+        <v>318956</v>
       </c>
       <c r="G40" t="n">
-        <v>322463</v>
+        <v>331131</v>
       </c>
       <c r="H40" t="n">
-        <v>1975</v>
+        <v>8370</v>
       </c>
       <c r="I40" t="n">
-        <v>105502</v>
+        <v>113892</v>
       </c>
       <c r="J40" t="n">
-        <v>107477</v>
+        <v>122262</v>
       </c>
       <c r="K40" t="n">
-        <v>0.5657</v>
+        <v>0.6875</v>
       </c>
       <c r="L40" t="n">
-        <v>0.3308</v>
+        <v>0.3571</v>
       </c>
       <c r="M40" t="n">
-        <v>0.3333</v>
+        <v>0.3692</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>202212</v>
+        <v>202302</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>20221201</t>
+          <t>20230201</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>4030</v>
+        <v>3874</v>
       </c>
       <c r="D41" t="n">
-        <v>51480</v>
+        <v>7365</v>
       </c>
       <c r="E41" t="n">
-        <v>51480</v>
+        <v>58845</v>
       </c>
       <c r="F41" t="n">
-        <v>267500</v>
+        <v>318971</v>
       </c>
       <c r="G41" t="n">
-        <v>318972</v>
+        <v>326336</v>
       </c>
       <c r="H41" t="n">
-        <v>42597</v>
+        <v>4945</v>
       </c>
       <c r="I41" t="n">
-        <v>114848</v>
+        <v>110993</v>
       </c>
       <c r="J41" t="n">
-        <v>157445</v>
+        <v>115938</v>
       </c>
       <c r="K41" t="n">
-        <v>0.8274</v>
+        <v>0.6714</v>
       </c>
       <c r="L41" t="n">
-        <v>0.4293</v>
+        <v>0.348</v>
       </c>
       <c r="M41" t="n">
-        <v>0.4936</v>
+        <v>0.3553</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>202211</v>
+        <v>202301</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>20221101</t>
+          <t>20230101</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>5003</v>
+        <v>3491</v>
       </c>
       <c r="D42" t="n">
-        <v>47450</v>
+        <v>3491</v>
       </c>
       <c r="E42" t="n">
-        <v>47450</v>
+        <v>54971</v>
       </c>
       <c r="F42" t="n">
-        <v>267519</v>
+        <v>318972</v>
       </c>
       <c r="G42" t="n">
-        <v>314962</v>
+        <v>322463</v>
       </c>
       <c r="H42" t="n">
-        <v>39008</v>
+        <v>1975</v>
       </c>
       <c r="I42" t="n">
-        <v>114448</v>
+        <v>105502</v>
       </c>
       <c r="J42" t="n">
-        <v>153457</v>
+        <v>107477</v>
       </c>
       <c r="K42" t="n">
-        <v>0.8221000000000001</v>
+        <v>0.5657</v>
       </c>
       <c r="L42" t="n">
-        <v>0.4278</v>
+        <v>0.3308</v>
       </c>
       <c r="M42" t="n">
-        <v>0.4872</v>
+        <v>0.3333</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>202210</v>
+        <v>202212</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>20221001</t>
+          <t>20221201</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>4889</v>
+        <v>4030</v>
       </c>
       <c r="D43" t="n">
-        <v>42447</v>
+        <v>51480</v>
       </c>
       <c r="E43" t="n">
-        <v>42447</v>
+        <v>51480</v>
       </c>
       <c r="F43" t="n">
-        <v>267549</v>
+        <v>267500</v>
       </c>
       <c r="G43" t="n">
-        <v>309991</v>
+        <v>318972</v>
       </c>
       <c r="H43" t="n">
-        <v>34928</v>
+        <v>42597</v>
       </c>
       <c r="I43" t="n">
-        <v>114037</v>
+        <v>114848</v>
       </c>
       <c r="J43" t="n">
-        <v>148966</v>
+        <v>157445</v>
       </c>
       <c r="K43" t="n">
-        <v>0.8229</v>
+        <v>0.8274</v>
       </c>
       <c r="L43" t="n">
-        <v>0.4262</v>
+        <v>0.4293</v>
       </c>
       <c r="M43" t="n">
-        <v>0.4805</v>
+        <v>0.4936</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>202209</v>
+        <v>202211</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>20220901</t>
+          <t>20221101</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>4947</v>
+        <v>5003</v>
       </c>
       <c r="D44" t="n">
-        <v>37558</v>
+        <v>47450</v>
       </c>
       <c r="E44" t="n">
-        <v>37558</v>
+        <v>47450</v>
       </c>
       <c r="F44" t="n">
-        <v>267549</v>
+        <v>267519</v>
       </c>
       <c r="G44" t="n">
-        <v>305102</v>
+        <v>314962</v>
       </c>
       <c r="H44" t="n">
-        <v>30883</v>
+        <v>39008</v>
       </c>
       <c r="I44" t="n">
-        <v>113595</v>
+        <v>114448</v>
       </c>
       <c r="J44" t="n">
-        <v>144479</v>
+        <v>153457</v>
       </c>
       <c r="K44" t="n">
-        <v>0.8223</v>
+        <v>0.8221000000000001</v>
       </c>
       <c r="L44" t="n">
-        <v>0.4246</v>
+        <v>0.4278</v>
       </c>
       <c r="M44" t="n">
-        <v>0.4735</v>
+        <v>0.4872</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>202208</v>
+        <v>202210</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>20220801</t>
+          <t>20221001</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>4823</v>
+        <v>4889</v>
       </c>
       <c r="D45" t="n">
-        <v>32611</v>
+        <v>42447</v>
       </c>
       <c r="E45" t="n">
-        <v>32611</v>
+        <v>42447</v>
       </c>
       <c r="F45" t="n">
-        <v>267580</v>
+        <v>267549</v>
       </c>
       <c r="G45" t="n">
-        <v>300187</v>
+        <v>309991</v>
       </c>
       <c r="H45" t="n">
-        <v>26588</v>
+        <v>34928</v>
       </c>
       <c r="I45" t="n">
-        <v>113115</v>
+        <v>114037</v>
       </c>
       <c r="J45" t="n">
-        <v>139704</v>
+        <v>148966</v>
       </c>
       <c r="K45" t="n">
-        <v>0.8153</v>
+        <v>0.8229</v>
       </c>
       <c r="L45" t="n">
-        <v>0.4227</v>
+        <v>0.4262</v>
       </c>
       <c r="M45" t="n">
-        <v>0.4654</v>
+        <v>0.4805</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>202207</v>
+        <v>202209</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>20220701</t>
+          <t>20220901</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>4091</v>
+        <v>4947</v>
       </c>
       <c r="D46" t="n">
-        <v>27788</v>
+        <v>37558</v>
       </c>
       <c r="E46" t="n">
-        <v>27788</v>
+        <v>37558</v>
       </c>
       <c r="F46" t="n">
-        <v>267583</v>
+        <v>267549</v>
       </c>
       <c r="G46" t="n">
-        <v>295369</v>
+        <v>305102</v>
       </c>
       <c r="H46" t="n">
-        <v>22607</v>
+        <v>30883</v>
       </c>
       <c r="I46" t="n">
-        <v>112524</v>
+        <v>113595</v>
       </c>
       <c r="J46" t="n">
-        <v>135132</v>
+        <v>144479</v>
       </c>
       <c r="K46" t="n">
-        <v>0.8136</v>
+        <v>0.8223</v>
       </c>
       <c r="L46" t="n">
-        <v>0.4205</v>
+        <v>0.4246</v>
       </c>
       <c r="M46" t="n">
-        <v>0.4575</v>
+        <v>0.4735</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>202206</v>
+        <v>202208</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>20220601</t>
+          <t>20220801</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>4200</v>
+        <v>4823</v>
       </c>
       <c r="D47" t="n">
-        <v>23697</v>
+        <v>32611</v>
       </c>
       <c r="E47" t="n">
-        <v>23697</v>
+        <v>32611</v>
       </c>
       <c r="F47" t="n">
-        <v>267588</v>
+        <v>267580</v>
       </c>
       <c r="G47" t="n">
-        <v>291284</v>
+        <v>300187</v>
       </c>
       <c r="H47" t="n">
-        <v>19087</v>
+        <v>26588</v>
       </c>
       <c r="I47" t="n">
-        <v>111816</v>
+        <v>113115</v>
       </c>
       <c r="J47" t="n">
-        <v>130903</v>
+        <v>139704</v>
       </c>
       <c r="K47" t="n">
-        <v>0.8055</v>
+        <v>0.8153</v>
       </c>
       <c r="L47" t="n">
-        <v>0.4179</v>
+        <v>0.4227</v>
       </c>
       <c r="M47" t="n">
-        <v>0.4494</v>
+        <v>0.4654</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>202205</v>
+        <v>202207</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>20220501</t>
+          <t>20220701</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>4447</v>
+        <v>4091</v>
       </c>
       <c r="D48" t="n">
-        <v>19497</v>
+        <v>27788</v>
       </c>
       <c r="E48" t="n">
-        <v>19497</v>
+        <v>27788</v>
       </c>
       <c r="F48" t="n">
-        <v>267586</v>
+        <v>267583</v>
       </c>
       <c r="G48" t="n">
-        <v>287082</v>
+        <v>295369</v>
       </c>
       <c r="H48" t="n">
-        <v>15602</v>
+        <v>22607</v>
       </c>
       <c r="I48" t="n">
-        <v>110837</v>
+        <v>112524</v>
       </c>
       <c r="J48" t="n">
-        <v>126439</v>
+        <v>135132</v>
       </c>
       <c r="K48" t="n">
-        <v>0.8002</v>
+        <v>0.8136</v>
       </c>
       <c r="L48" t="n">
-        <v>0.4142</v>
+        <v>0.4205</v>
       </c>
       <c r="M48" t="n">
-        <v>0.4404</v>
+        <v>0.4575</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>202204</v>
+        <v>202206</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>20220401</t>
+          <t>20220601</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>3923</v>
+        <v>4200</v>
       </c>
       <c r="D49" t="n">
-        <v>15050</v>
+        <v>23697</v>
       </c>
       <c r="E49" t="n">
-        <v>15050</v>
+        <v>23697</v>
       </c>
       <c r="F49" t="n">
-        <v>267609</v>
+        <v>267588</v>
       </c>
       <c r="G49" t="n">
-        <v>282658</v>
+        <v>291284</v>
       </c>
       <c r="H49" t="n">
-        <v>11960</v>
+        <v>19087</v>
       </c>
       <c r="I49" t="n">
-        <v>109488</v>
+        <v>111816</v>
       </c>
       <c r="J49" t="n">
-        <v>121448</v>
+        <v>130903</v>
       </c>
       <c r="K49" t="n">
-        <v>0.7947</v>
+        <v>0.8055</v>
       </c>
       <c r="L49" t="n">
-        <v>0.4091</v>
+        <v>0.4179</v>
       </c>
       <c r="M49" t="n">
-        <v>0.4297</v>
+        <v>0.4494</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>202203</v>
+        <v>202205</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>20220301</t>
+          <t>20220501</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>4781</v>
+        <v>4447</v>
       </c>
       <c r="D50" t="n">
-        <v>11127</v>
+        <v>19497</v>
       </c>
       <c r="E50" t="n">
-        <v>11127</v>
+        <v>19497</v>
       </c>
       <c r="F50" t="n">
-        <v>267609</v>
+        <v>267586</v>
       </c>
       <c r="G50" t="n">
-        <v>278735</v>
+        <v>287082</v>
       </c>
       <c r="H50" t="n">
-        <v>8402</v>
+        <v>15602</v>
       </c>
       <c r="I50" t="n">
-        <v>107634</v>
+        <v>110837</v>
       </c>
       <c r="J50" t="n">
-        <v>116036</v>
+        <v>126439</v>
       </c>
       <c r="K50" t="n">
-        <v>0.7551</v>
+        <v>0.8002</v>
       </c>
       <c r="L50" t="n">
-        <v>0.4022</v>
+        <v>0.4142</v>
       </c>
       <c r="M50" t="n">
-        <v>0.4163</v>
+        <v>0.4404</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>202202</v>
+        <v>202204</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>20220201</t>
+          <t>20220401</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>3590</v>
+        <v>3923</v>
       </c>
       <c r="D51" t="n">
-        <v>6346</v>
+        <v>15050</v>
       </c>
       <c r="E51" t="n">
-        <v>6346</v>
+        <v>15050</v>
       </c>
       <c r="F51" t="n">
-        <v>267627</v>
+        <v>267609</v>
       </c>
       <c r="G51" t="n">
-        <v>273973</v>
+        <v>282658</v>
       </c>
       <c r="H51" t="n">
-        <v>4531</v>
+        <v>11960</v>
       </c>
       <c r="I51" t="n">
-        <v>104493</v>
+        <v>109488</v>
       </c>
       <c r="J51" t="n">
-        <v>109024</v>
+        <v>121448</v>
       </c>
       <c r="K51" t="n">
-        <v>0.714</v>
+        <v>0.7947</v>
       </c>
       <c r="L51" t="n">
-        <v>0.3904</v>
+        <v>0.4091</v>
       </c>
       <c r="M51" t="n">
-        <v>0.3979</v>
+        <v>0.4297</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
+        <v>202203</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>20220301</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>4781</v>
+      </c>
+      <c r="D52" t="n">
+        <v>11127</v>
+      </c>
+      <c r="E52" t="n">
+        <v>11127</v>
+      </c>
+      <c r="F52" t="n">
+        <v>267609</v>
+      </c>
+      <c r="G52" t="n">
+        <v>278735</v>
+      </c>
+      <c r="H52" t="n">
+        <v>8402</v>
+      </c>
+      <c r="I52" t="n">
+        <v>107634</v>
+      </c>
+      <c r="J52" t="n">
+        <v>116036</v>
+      </c>
+      <c r="K52" t="n">
+        <v>0.7551</v>
+      </c>
+      <c r="L52" t="n">
+        <v>0.4022</v>
+      </c>
+      <c r="M52" t="n">
+        <v>0.4163</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>202202</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>20220201</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>3590</v>
+      </c>
+      <c r="D53" t="n">
+        <v>6346</v>
+      </c>
+      <c r="E53" t="n">
+        <v>6346</v>
+      </c>
+      <c r="F53" t="n">
+        <v>267627</v>
+      </c>
+      <c r="G53" t="n">
+        <v>273973</v>
+      </c>
+      <c r="H53" t="n">
+        <v>4531</v>
+      </c>
+      <c r="I53" t="n">
+        <v>104493</v>
+      </c>
+      <c r="J53" t="n">
+        <v>109024</v>
+      </c>
+      <c r="K53" t="n">
+        <v>0.714</v>
+      </c>
+      <c r="L53" t="n">
+        <v>0.3904</v>
+      </c>
+      <c r="M53" t="n">
+        <v>0.3979</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
         <v>202201</v>
       </c>
-      <c r="B52" t="inlineStr">
+      <c r="B54" t="inlineStr">
         <is>
           <t>20220101</t>
         </is>
       </c>
-      <c r="C52" t="n">
+      <c r="C54" t="n">
         <v>2756</v>
       </c>
-      <c r="D52" t="n">
+      <c r="D54" t="n">
         <v>2756</v>
       </c>
-      <c r="E52" t="n">
+      <c r="E54" t="n">
         <v>2756</v>
       </c>
-      <c r="F52" t="n">
+      <c r="F54" t="n">
         <v>267632</v>
       </c>
-      <c r="G52" t="n">
+      <c r="G54" t="n">
         <v>270388</v>
       </c>
-      <c r="H52" t="n">
+      <c r="H54" t="n">
         <v>1628</v>
       </c>
-      <c r="I52" t="n">
+      <c r="I54" t="n">
         <v>98510</v>
       </c>
-      <c r="J52" t="n">
+      <c r="J54" t="n">
         <v>100138</v>
       </c>
-      <c r="K52" t="n">
+      <c r="K54" t="n">
         <v>0.5907</v>
       </c>
-      <c r="L52" t="n">
+      <c r="L54" t="n">
         <v>0.3681</v>
       </c>
-      <c r="M52" t="n">
+      <c r="M54" t="n">
         <v>0.3703</v>
       </c>
     </row>

--- a/main_data/evolucion_vinculacion_y_uso_adquirencia_1_a_1.xlsx
+++ b/main_data/evolucion_vinculacion_y_uso_adquirencia_1_a_1.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M54"/>
+  <dimension ref="A1:M56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -497,2280 +497,2366 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>202605</v>
+        <v>202607</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>20260501</t>
+          <t>20260701</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3364</v>
+        <v>3812</v>
       </c>
       <c r="D2" t="n">
-        <v>16859</v>
+        <v>23778</v>
       </c>
       <c r="E2" t="n">
-        <v>198590</v>
+        <v>205509</v>
       </c>
       <c r="F2" t="n">
-        <v>448057</v>
+        <v>447611</v>
       </c>
       <c r="G2" t="n">
-        <v>464916</v>
+        <v>471385</v>
       </c>
       <c r="H2" t="n">
-        <v>8447</v>
+        <v>12093</v>
       </c>
       <c r="I2" t="n">
-        <v>108073</v>
+        <v>109345</v>
       </c>
       <c r="J2" t="n">
-        <v>116521</v>
+        <v>121439</v>
       </c>
       <c r="K2" t="n">
-        <v>0.501</v>
+        <v>0.5086000000000001</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2412</v>
+        <v>0.2443</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2506</v>
+        <v>0.2576</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>202604</v>
+        <v>202606</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>20260401</t>
+          <t>20260601</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>3739</v>
+        <v>3107</v>
       </c>
       <c r="D3" t="n">
-        <v>13495</v>
+        <v>19966</v>
       </c>
       <c r="E3" t="n">
-        <v>195226</v>
+        <v>201697</v>
       </c>
       <c r="F3" t="n">
-        <v>448056</v>
+        <v>447619</v>
       </c>
       <c r="G3" t="n">
-        <v>461551</v>
+        <v>467583</v>
       </c>
       <c r="H3" t="n">
-        <v>6523</v>
+        <v>10280</v>
       </c>
       <c r="I3" t="n">
-        <v>107059</v>
+        <v>108755</v>
       </c>
       <c r="J3" t="n">
-        <v>113583</v>
+        <v>119036</v>
       </c>
       <c r="K3" t="n">
-        <v>0.4834</v>
+        <v>0.5149</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2389</v>
+        <v>0.243</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2461</v>
+        <v>0.2546</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>202603</v>
+        <v>202605</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>20260301</t>
+          <t>20260501</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>3887</v>
+        <v>3364</v>
       </c>
       <c r="D4" t="n">
-        <v>9756</v>
+        <v>16859</v>
       </c>
       <c r="E4" t="n">
-        <v>191487</v>
+        <v>198590</v>
       </c>
       <c r="F4" t="n">
-        <v>448074</v>
+        <v>448057</v>
       </c>
       <c r="G4" t="n">
-        <v>457831</v>
+        <v>464916</v>
       </c>
       <c r="H4" t="n">
-        <v>4602</v>
+        <v>8447</v>
       </c>
       <c r="I4" t="n">
-        <v>105678</v>
+        <v>108073</v>
       </c>
       <c r="J4" t="n">
-        <v>110281</v>
+        <v>116521</v>
       </c>
       <c r="K4" t="n">
-        <v>0.4717</v>
+        <v>0.501</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2358</v>
+        <v>0.2412</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2409</v>
+        <v>0.2506</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>202602</v>
+        <v>202604</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>20260201</t>
+          <t>20260401</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>3200</v>
+        <v>3739</v>
       </c>
       <c r="D5" t="n">
-        <v>5869</v>
+        <v>13495</v>
       </c>
       <c r="E5" t="n">
-        <v>187600</v>
+        <v>195226</v>
       </c>
       <c r="F5" t="n">
-        <v>448099</v>
+        <v>448056</v>
       </c>
       <c r="G5" t="n">
-        <v>453969</v>
+        <v>461551</v>
       </c>
       <c r="H5" t="n">
-        <v>2617</v>
+        <v>6523</v>
       </c>
       <c r="I5" t="n">
-        <v>103470</v>
+        <v>107059</v>
       </c>
       <c r="J5" t="n">
-        <v>106088</v>
+        <v>113583</v>
       </c>
       <c r="K5" t="n">
-        <v>0.4459</v>
+        <v>0.4834</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2309</v>
+        <v>0.2389</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2337</v>
+        <v>0.2461</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>202601</v>
+        <v>202603</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>20260101</t>
+          <t>20260301</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2669</v>
+        <v>3887</v>
       </c>
       <c r="D6" t="n">
-        <v>2669</v>
+        <v>9756</v>
       </c>
       <c r="E6" t="n">
-        <v>184400</v>
+        <v>191487</v>
       </c>
       <c r="F6" t="n">
-        <v>448103</v>
+        <v>448074</v>
       </c>
       <c r="G6" t="n">
-        <v>450772</v>
+        <v>457831</v>
       </c>
       <c r="H6" t="n">
-        <v>1004</v>
+        <v>4602</v>
       </c>
       <c r="I6" t="n">
-        <v>98960</v>
+        <v>105678</v>
       </c>
       <c r="J6" t="n">
-        <v>99964</v>
+        <v>110281</v>
       </c>
       <c r="K6" t="n">
-        <v>0.3762</v>
+        <v>0.4717</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2208</v>
+        <v>0.2358</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2218</v>
+        <v>0.2409</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>202512</v>
+        <v>202602</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>20251201</t>
+          <t>20260201</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3412</v>
+        <v>3200</v>
       </c>
       <c r="D7" t="n">
-        <v>38305</v>
+        <v>5869</v>
       </c>
       <c r="E7" t="n">
-        <v>181731</v>
+        <v>187600</v>
       </c>
       <c r="F7" t="n">
-        <v>409803</v>
+        <v>448099</v>
       </c>
       <c r="G7" t="n">
-        <v>448104</v>
+        <v>453969</v>
       </c>
       <c r="H7" t="n">
-        <v>24455</v>
+        <v>2617</v>
       </c>
       <c r="I7" t="n">
-        <v>113080</v>
+        <v>103470</v>
       </c>
       <c r="J7" t="n">
-        <v>137535</v>
+        <v>106088</v>
       </c>
       <c r="K7" t="n">
-        <v>0.6384</v>
+        <v>0.4459</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2759</v>
+        <v>0.2309</v>
       </c>
       <c r="M7" t="n">
-        <v>0.3069</v>
+        <v>0.2337</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>202511</v>
+        <v>202601</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>20251101</t>
+          <t>20260101</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>3284</v>
+        <v>2669</v>
       </c>
       <c r="D8" t="n">
-        <v>34893</v>
+        <v>2669</v>
       </c>
       <c r="E8" t="n">
-        <v>178319</v>
+        <v>184400</v>
       </c>
       <c r="F8" t="n">
-        <v>409832</v>
+        <v>448103</v>
       </c>
       <c r="G8" t="n">
-        <v>444725</v>
+        <v>450772</v>
       </c>
       <c r="H8" t="n">
-        <v>22119</v>
+        <v>1004</v>
       </c>
       <c r="I8" t="n">
-        <v>112697</v>
+        <v>98960</v>
       </c>
       <c r="J8" t="n">
-        <v>134816</v>
+        <v>99964</v>
       </c>
       <c r="K8" t="n">
-        <v>0.6339</v>
+        <v>0.3762</v>
       </c>
       <c r="L8" t="n">
-        <v>0.275</v>
+        <v>0.2208</v>
       </c>
       <c r="M8" t="n">
-        <v>0.3031</v>
+        <v>0.2218</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>202510</v>
+        <v>202512</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>20251001</t>
+          <t>20251201</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>3759</v>
+        <v>3412</v>
       </c>
       <c r="D9" t="n">
-        <v>31609</v>
+        <v>38305</v>
       </c>
       <c r="E9" t="n">
-        <v>175035</v>
+        <v>181731</v>
       </c>
       <c r="F9" t="n">
-        <v>409896</v>
+        <v>409803</v>
       </c>
       <c r="G9" t="n">
-        <v>441505</v>
+        <v>448104</v>
       </c>
       <c r="H9" t="n">
-        <v>20079</v>
+        <v>24455</v>
       </c>
       <c r="I9" t="n">
-        <v>112384</v>
+        <v>113080</v>
       </c>
       <c r="J9" t="n">
-        <v>132463</v>
+        <v>137535</v>
       </c>
       <c r="K9" t="n">
-        <v>0.6352</v>
+        <v>0.6384</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2742</v>
+        <v>0.2759</v>
       </c>
       <c r="M9" t="n">
-        <v>0.3</v>
+        <v>0.3069</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>202509</v>
+        <v>202511</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>20250901</t>
+          <t>20251101</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>3640</v>
+        <v>3284</v>
       </c>
       <c r="D10" t="n">
-        <v>27850</v>
+        <v>34893</v>
       </c>
       <c r="E10" t="n">
-        <v>171276</v>
+        <v>178319</v>
       </c>
       <c r="F10" t="n">
-        <v>409900</v>
+        <v>409832</v>
       </c>
       <c r="G10" t="n">
-        <v>437750</v>
+        <v>444725</v>
       </c>
       <c r="H10" t="n">
-        <v>17741</v>
+        <v>22119</v>
       </c>
       <c r="I10" t="n">
-        <v>111995</v>
+        <v>112697</v>
       </c>
       <c r="J10" t="n">
-        <v>129736</v>
+        <v>134816</v>
       </c>
       <c r="K10" t="n">
-        <v>0.637</v>
+        <v>0.6339</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2732</v>
+        <v>0.275</v>
       </c>
       <c r="M10" t="n">
-        <v>0.2964</v>
+        <v>0.3031</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>202508</v>
+        <v>202510</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>20250801</t>
+          <t>20251001</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2970</v>
+        <v>3759</v>
       </c>
       <c r="D11" t="n">
-        <v>24210</v>
+        <v>31609</v>
       </c>
       <c r="E11" t="n">
-        <v>167636</v>
+        <v>175035</v>
       </c>
       <c r="F11" t="n">
-        <v>409903</v>
+        <v>409896</v>
       </c>
       <c r="G11" t="n">
-        <v>434113</v>
+        <v>441505</v>
       </c>
       <c r="H11" t="n">
-        <v>15543</v>
+        <v>20079</v>
       </c>
       <c r="I11" t="n">
-        <v>111498</v>
+        <v>112384</v>
       </c>
       <c r="J11" t="n">
-        <v>127041</v>
+        <v>132463</v>
       </c>
       <c r="K11" t="n">
-        <v>0.642</v>
+        <v>0.6352</v>
       </c>
       <c r="L11" t="n">
-        <v>0.272</v>
+        <v>0.2742</v>
       </c>
       <c r="M11" t="n">
-        <v>0.2926</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>202507</v>
+        <v>202509</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>20250701</t>
+          <t>20250901</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>3699</v>
+        <v>3640</v>
       </c>
       <c r="D12" t="n">
-        <v>21240</v>
+        <v>27850</v>
       </c>
       <c r="E12" t="n">
-        <v>164666</v>
+        <v>171276</v>
       </c>
       <c r="F12" t="n">
-        <v>409905</v>
+        <v>409900</v>
       </c>
       <c r="G12" t="n">
-        <v>431145</v>
+        <v>437750</v>
       </c>
       <c r="H12" t="n">
-        <v>13549</v>
+        <v>17741</v>
       </c>
       <c r="I12" t="n">
-        <v>110935</v>
+        <v>111995</v>
       </c>
       <c r="J12" t="n">
-        <v>124484</v>
+        <v>129736</v>
       </c>
       <c r="K12" t="n">
-        <v>0.6379</v>
+        <v>0.637</v>
       </c>
       <c r="L12" t="n">
-        <v>0.2706</v>
+        <v>0.2732</v>
       </c>
       <c r="M12" t="n">
-        <v>0.2887</v>
+        <v>0.2964</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>202506</v>
+        <v>202508</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>20250601</t>
+          <t>20250801</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>3151</v>
+        <v>2970</v>
       </c>
       <c r="D13" t="n">
-        <v>17541</v>
+        <v>24210</v>
       </c>
       <c r="E13" t="n">
-        <v>160967</v>
+        <v>167636</v>
       </c>
       <c r="F13" t="n">
-        <v>409922</v>
+        <v>409903</v>
       </c>
       <c r="G13" t="n">
-        <v>427463</v>
+        <v>434113</v>
       </c>
       <c r="H13" t="n">
-        <v>11155</v>
+        <v>15543</v>
       </c>
       <c r="I13" t="n">
-        <v>110174</v>
+        <v>111498</v>
       </c>
       <c r="J13" t="n">
-        <v>121329</v>
+        <v>127041</v>
       </c>
       <c r="K13" t="n">
-        <v>0.6359</v>
+        <v>0.642</v>
       </c>
       <c r="L13" t="n">
-        <v>0.2688</v>
+        <v>0.272</v>
       </c>
       <c r="M13" t="n">
-        <v>0.2838</v>
+        <v>0.2926</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>202505</v>
+        <v>202507</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>20250501</t>
+          <t>20250701</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>3231</v>
+        <v>3699</v>
       </c>
       <c r="D14" t="n">
-        <v>14390</v>
+        <v>21240</v>
       </c>
       <c r="E14" t="n">
-        <v>157816</v>
+        <v>164666</v>
       </c>
       <c r="F14" t="n">
-        <v>409925</v>
+        <v>409905</v>
       </c>
       <c r="G14" t="n">
-        <v>424315</v>
+        <v>431145</v>
       </c>
       <c r="H14" t="n">
-        <v>9084</v>
+        <v>13549</v>
       </c>
       <c r="I14" t="n">
-        <v>109362</v>
+        <v>110935</v>
       </c>
       <c r="J14" t="n">
-        <v>118446</v>
+        <v>124484</v>
       </c>
       <c r="K14" t="n">
-        <v>0.6313</v>
+        <v>0.6379</v>
       </c>
       <c r="L14" t="n">
-        <v>0.2668</v>
+        <v>0.2706</v>
       </c>
       <c r="M14" t="n">
-        <v>0.2791</v>
+        <v>0.2887</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>202504</v>
+        <v>202506</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>20250401</t>
+          <t>20250601</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>3317</v>
+        <v>3151</v>
       </c>
       <c r="D15" t="n">
-        <v>11159</v>
+        <v>17541</v>
       </c>
       <c r="E15" t="n">
-        <v>154585</v>
+        <v>160967</v>
       </c>
       <c r="F15" t="n">
-        <v>409928</v>
+        <v>409922</v>
       </c>
       <c r="G15" t="n">
-        <v>421087</v>
+        <v>427463</v>
       </c>
       <c r="H15" t="n">
-        <v>6861</v>
+        <v>11155</v>
       </c>
       <c r="I15" t="n">
-        <v>108111</v>
+        <v>110174</v>
       </c>
       <c r="J15" t="n">
-        <v>114972</v>
+        <v>121329</v>
       </c>
       <c r="K15" t="n">
-        <v>0.6148</v>
+        <v>0.6359</v>
       </c>
       <c r="L15" t="n">
-        <v>0.2637</v>
+        <v>0.2688</v>
       </c>
       <c r="M15" t="n">
-        <v>0.273</v>
+        <v>0.2838</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>202503</v>
+        <v>202505</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>20250301</t>
+          <t>20250501</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>2887</v>
+        <v>3231</v>
       </c>
       <c r="D16" t="n">
-        <v>7842</v>
+        <v>14390</v>
       </c>
       <c r="E16" t="n">
-        <v>151268</v>
+        <v>157816</v>
       </c>
       <c r="F16" t="n">
-        <v>409953</v>
+        <v>409925</v>
       </c>
       <c r="G16" t="n">
-        <v>417795</v>
+        <v>424315</v>
       </c>
       <c r="H16" t="n">
-        <v>4674</v>
+        <v>9084</v>
       </c>
       <c r="I16" t="n">
-        <v>106615</v>
+        <v>109362</v>
       </c>
       <c r="J16" t="n">
-        <v>111289</v>
+        <v>118446</v>
       </c>
       <c r="K16" t="n">
-        <v>0.596</v>
+        <v>0.6313</v>
       </c>
       <c r="L16" t="n">
-        <v>0.2601</v>
+        <v>0.2668</v>
       </c>
       <c r="M16" t="n">
-        <v>0.2664</v>
+        <v>0.2791</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>202502</v>
+        <v>202504</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>20250201</t>
+          <t>20250401</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>2691</v>
+        <v>3317</v>
       </c>
       <c r="D17" t="n">
-        <v>4955</v>
+        <v>11159</v>
       </c>
       <c r="E17" t="n">
-        <v>148381</v>
+        <v>154585</v>
       </c>
       <c r="F17" t="n">
-        <v>409938</v>
+        <v>409928</v>
       </c>
       <c r="G17" t="n">
-        <v>414893</v>
+        <v>421087</v>
       </c>
       <c r="H17" t="n">
-        <v>2828</v>
+        <v>6861</v>
       </c>
       <c r="I17" t="n">
-        <v>104133</v>
+        <v>108111</v>
       </c>
       <c r="J17" t="n">
-        <v>106961</v>
+        <v>114972</v>
       </c>
       <c r="K17" t="n">
-        <v>0.5707</v>
+        <v>0.6148</v>
       </c>
       <c r="L17" t="n">
-        <v>0.254</v>
+        <v>0.2637</v>
       </c>
       <c r="M17" t="n">
-        <v>0.2578</v>
+        <v>0.273</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>202501</v>
+        <v>202503</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>20250101</t>
+          <t>20250301</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>2264</v>
+        <v>2887</v>
       </c>
       <c r="D18" t="n">
-        <v>2264</v>
+        <v>7842</v>
       </c>
       <c r="E18" t="n">
-        <v>145690</v>
+        <v>151268</v>
       </c>
       <c r="F18" t="n">
-        <v>410060</v>
+        <v>409953</v>
       </c>
       <c r="G18" t="n">
-        <v>412324</v>
+        <v>417795</v>
       </c>
       <c r="H18" t="n">
-        <v>1159</v>
+        <v>4674</v>
       </c>
       <c r="I18" t="n">
-        <v>99434</v>
+        <v>106615</v>
       </c>
       <c r="J18" t="n">
-        <v>100593</v>
+        <v>111289</v>
       </c>
       <c r="K18" t="n">
-        <v>0.5119</v>
+        <v>0.596</v>
       </c>
       <c r="L18" t="n">
-        <v>0.2425</v>
+        <v>0.2601</v>
       </c>
       <c r="M18" t="n">
-        <v>0.244</v>
+        <v>0.2664</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>202412</v>
+        <v>202502</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>20241201</t>
+          <t>20250201</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>2910</v>
+        <v>2691</v>
       </c>
       <c r="D19" t="n">
-        <v>38529</v>
+        <v>4955</v>
       </c>
       <c r="E19" t="n">
-        <v>143426</v>
+        <v>148381</v>
       </c>
       <c r="F19" t="n">
-        <v>371557</v>
+        <v>409938</v>
       </c>
       <c r="G19" t="n">
-        <v>410078</v>
+        <v>414893</v>
       </c>
       <c r="H19" t="n">
-        <v>28109</v>
+        <v>2828</v>
       </c>
       <c r="I19" t="n">
-        <v>122366</v>
+        <v>104133</v>
       </c>
       <c r="J19" t="n">
-        <v>150475</v>
+        <v>106961</v>
       </c>
       <c r="K19" t="n">
-        <v>0.7296</v>
+        <v>0.5707</v>
       </c>
       <c r="L19" t="n">
-        <v>0.3293</v>
+        <v>0.254</v>
       </c>
       <c r="M19" t="n">
-        <v>0.3669</v>
+        <v>0.2578</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>202411</v>
+        <v>202501</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>20241101</t>
+          <t>20250101</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>2980</v>
+        <v>2264</v>
       </c>
       <c r="D20" t="n">
-        <v>35619</v>
+        <v>2264</v>
       </c>
       <c r="E20" t="n">
-        <v>140516</v>
+        <v>145690</v>
       </c>
       <c r="F20" t="n">
-        <v>371563</v>
+        <v>410060</v>
       </c>
       <c r="G20" t="n">
-        <v>407176</v>
+        <v>412324</v>
       </c>
       <c r="H20" t="n">
-        <v>25789</v>
+        <v>1159</v>
       </c>
       <c r="I20" t="n">
-        <v>122024</v>
+        <v>99434</v>
       </c>
       <c r="J20" t="n">
-        <v>147813</v>
+        <v>100593</v>
       </c>
       <c r="K20" t="n">
-        <v>0.724</v>
+        <v>0.5119</v>
       </c>
       <c r="L20" t="n">
-        <v>0.3284</v>
+        <v>0.2425</v>
       </c>
       <c r="M20" t="n">
-        <v>0.363</v>
+        <v>0.244</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>202410</v>
+        <v>202412</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>20241001</t>
+          <t>20241201</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>3113</v>
+        <v>2910</v>
       </c>
       <c r="D21" t="n">
-        <v>32639</v>
+        <v>38529</v>
       </c>
       <c r="E21" t="n">
-        <v>137536</v>
+        <v>143426</v>
       </c>
       <c r="F21" t="n">
-        <v>371563</v>
+        <v>371557</v>
       </c>
       <c r="G21" t="n">
-        <v>404196</v>
+        <v>410078</v>
       </c>
       <c r="H21" t="n">
-        <v>23547</v>
+        <v>28109</v>
       </c>
       <c r="I21" t="n">
-        <v>121582</v>
+        <v>122366</v>
       </c>
       <c r="J21" t="n">
-        <v>145129</v>
+        <v>150475</v>
       </c>
       <c r="K21" t="n">
-        <v>0.7214</v>
+        <v>0.7296</v>
       </c>
       <c r="L21" t="n">
-        <v>0.3272</v>
+        <v>0.3293</v>
       </c>
       <c r="M21" t="n">
-        <v>0.3591</v>
+        <v>0.3669</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>202409</v>
+        <v>202411</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>20240901</t>
+          <t>20241101</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>3706</v>
+        <v>2980</v>
       </c>
       <c r="D22" t="n">
-        <v>29526</v>
+        <v>35619</v>
       </c>
       <c r="E22" t="n">
-        <v>134423</v>
+        <v>140516</v>
       </c>
       <c r="F22" t="n">
-        <v>371574</v>
+        <v>371563</v>
       </c>
       <c r="G22" t="n">
-        <v>401097</v>
+        <v>407176</v>
       </c>
       <c r="H22" t="n">
-        <v>21278</v>
+        <v>25789</v>
       </c>
       <c r="I22" t="n">
-        <v>121138</v>
+        <v>122024</v>
       </c>
       <c r="J22" t="n">
-        <v>142416</v>
+        <v>147813</v>
       </c>
       <c r="K22" t="n">
-        <v>0.7207</v>
+        <v>0.724</v>
       </c>
       <c r="L22" t="n">
-        <v>0.326</v>
+        <v>0.3284</v>
       </c>
       <c r="M22" t="n">
-        <v>0.3551</v>
+        <v>0.363</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>202408</v>
+        <v>202410</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>20240801</t>
+          <t>20241001</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>3077</v>
+        <v>3113</v>
       </c>
       <c r="D23" t="n">
-        <v>25820</v>
+        <v>32639</v>
       </c>
       <c r="E23" t="n">
-        <v>130717</v>
+        <v>137536</v>
       </c>
       <c r="F23" t="n">
-        <v>371579</v>
+        <v>371563</v>
       </c>
       <c r="G23" t="n">
-        <v>397396</v>
+        <v>404196</v>
       </c>
       <c r="H23" t="n">
-        <v>18489</v>
+        <v>23547</v>
       </c>
       <c r="I23" t="n">
-        <v>120662</v>
+        <v>121582</v>
       </c>
       <c r="J23" t="n">
-        <v>139151</v>
+        <v>145129</v>
       </c>
       <c r="K23" t="n">
-        <v>0.7161</v>
+        <v>0.7214</v>
       </c>
       <c r="L23" t="n">
-        <v>0.3247</v>
+        <v>0.3272</v>
       </c>
       <c r="M23" t="n">
-        <v>0.3502</v>
+        <v>0.3591</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>202407</v>
+        <v>202409</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>20240701</t>
+          <t>20240901</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>3250</v>
+        <v>3706</v>
       </c>
       <c r="D24" t="n">
-        <v>22743</v>
+        <v>29526</v>
       </c>
       <c r="E24" t="n">
-        <v>127640</v>
+        <v>134423</v>
       </c>
       <c r="F24" t="n">
-        <v>371589</v>
+        <v>371574</v>
       </c>
       <c r="G24" t="n">
-        <v>394329</v>
+        <v>401097</v>
       </c>
       <c r="H24" t="n">
-        <v>16281</v>
+        <v>21278</v>
       </c>
       <c r="I24" t="n">
-        <v>120039</v>
+        <v>121138</v>
       </c>
       <c r="J24" t="n">
-        <v>136320</v>
+        <v>142416</v>
       </c>
       <c r="K24" t="n">
-        <v>0.7159</v>
+        <v>0.7207</v>
       </c>
       <c r="L24" t="n">
-        <v>0.323</v>
+        <v>0.326</v>
       </c>
       <c r="M24" t="n">
-        <v>0.3457</v>
+        <v>0.3551</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>202406</v>
+        <v>202408</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>20240601</t>
+          <t>20240801</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>2683</v>
+        <v>3077</v>
       </c>
       <c r="D25" t="n">
-        <v>19493</v>
+        <v>25820</v>
       </c>
       <c r="E25" t="n">
-        <v>124390</v>
+        <v>130717</v>
       </c>
       <c r="F25" t="n">
-        <v>371581</v>
+        <v>371579</v>
       </c>
       <c r="G25" t="n">
-        <v>391072</v>
+        <v>397396</v>
       </c>
       <c r="H25" t="n">
-        <v>14112</v>
+        <v>18489</v>
       </c>
       <c r="I25" t="n">
-        <v>119205</v>
+        <v>120662</v>
       </c>
       <c r="J25" t="n">
-        <v>133317</v>
+        <v>139151</v>
       </c>
       <c r="K25" t="n">
-        <v>0.724</v>
+        <v>0.7161</v>
       </c>
       <c r="L25" t="n">
-        <v>0.3208</v>
+        <v>0.3247</v>
       </c>
       <c r="M25" t="n">
-        <v>0.3409</v>
+        <v>0.3502</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>202405</v>
+        <v>202407</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>20240501</t>
+          <t>20240701</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>2946</v>
+        <v>3250</v>
       </c>
       <c r="D26" t="n">
-        <v>16810</v>
+        <v>22743</v>
       </c>
       <c r="E26" t="n">
-        <v>121707</v>
+        <v>127640</v>
       </c>
       <c r="F26" t="n">
-        <v>371587</v>
+        <v>371589</v>
       </c>
       <c r="G26" t="n">
-        <v>388397</v>
+        <v>394329</v>
       </c>
       <c r="H26" t="n">
-        <v>12260</v>
+        <v>16281</v>
       </c>
       <c r="I26" t="n">
-        <v>118299</v>
+        <v>120039</v>
       </c>
       <c r="J26" t="n">
-        <v>130559</v>
+        <v>136320</v>
       </c>
       <c r="K26" t="n">
-        <v>0.7292999999999999</v>
+        <v>0.7159</v>
       </c>
       <c r="L26" t="n">
-        <v>0.3184</v>
+        <v>0.323</v>
       </c>
       <c r="M26" t="n">
-        <v>0.3361</v>
+        <v>0.3457</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>202404</v>
+        <v>202406</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>20240401</t>
+          <t>20240601</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>3198</v>
+        <v>2683</v>
       </c>
       <c r="D27" t="n">
-        <v>13864</v>
+        <v>19493</v>
       </c>
       <c r="E27" t="n">
-        <v>118761</v>
+        <v>124390</v>
       </c>
       <c r="F27" t="n">
-        <v>371594</v>
+        <v>371581</v>
       </c>
       <c r="G27" t="n">
-        <v>385458</v>
+        <v>391072</v>
       </c>
       <c r="H27" t="n">
-        <v>9995</v>
+        <v>14112</v>
       </c>
       <c r="I27" t="n">
-        <v>116888</v>
+        <v>119205</v>
       </c>
       <c r="J27" t="n">
-        <v>126883</v>
+        <v>133317</v>
       </c>
       <c r="K27" t="n">
-        <v>0.7209</v>
+        <v>0.724</v>
       </c>
       <c r="L27" t="n">
-        <v>0.3146</v>
+        <v>0.3208</v>
       </c>
       <c r="M27" t="n">
-        <v>0.3292</v>
+        <v>0.3409</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>202403</v>
+        <v>202405</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>20240301</t>
+          <t>20240501</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>3430</v>
+        <v>2946</v>
       </c>
       <c r="D28" t="n">
-        <v>10666</v>
+        <v>16810</v>
       </c>
       <c r="E28" t="n">
-        <v>115563</v>
+        <v>121707</v>
       </c>
       <c r="F28" t="n">
-        <v>371607</v>
+        <v>371587</v>
       </c>
       <c r="G28" t="n">
-        <v>382273</v>
+        <v>388397</v>
       </c>
       <c r="H28" t="n">
-        <v>7763</v>
+        <v>12260</v>
       </c>
       <c r="I28" t="n">
-        <v>115020</v>
+        <v>118299</v>
       </c>
       <c r="J28" t="n">
-        <v>122783</v>
+        <v>130559</v>
       </c>
       <c r="K28" t="n">
-        <v>0.7278</v>
+        <v>0.7292999999999999</v>
       </c>
       <c r="L28" t="n">
-        <v>0.3095</v>
+        <v>0.3184</v>
       </c>
       <c r="M28" t="n">
-        <v>0.3212</v>
+        <v>0.3361</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>202402</v>
+        <v>202404</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>20240201</t>
+          <t>20240401</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>4092</v>
+        <v>3198</v>
       </c>
       <c r="D29" t="n">
-        <v>7236</v>
+        <v>13864</v>
       </c>
       <c r="E29" t="n">
-        <v>112133</v>
+        <v>118761</v>
       </c>
       <c r="F29" t="n">
-        <v>371597</v>
+        <v>371594</v>
       </c>
       <c r="G29" t="n">
-        <v>378833</v>
+        <v>385458</v>
       </c>
       <c r="H29" t="n">
-        <v>4888</v>
+        <v>9995</v>
       </c>
       <c r="I29" t="n">
-        <v>112247</v>
+        <v>116888</v>
       </c>
       <c r="J29" t="n">
-        <v>117135</v>
+        <v>126883</v>
       </c>
       <c r="K29" t="n">
-        <v>0.6755</v>
+        <v>0.7209</v>
       </c>
       <c r="L29" t="n">
-        <v>0.3021</v>
+        <v>0.3146</v>
       </c>
       <c r="M29" t="n">
-        <v>0.3092</v>
+        <v>0.3292</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>202401</v>
+        <v>202403</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>20240101</t>
+          <t>20240301</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>3144</v>
+        <v>3430</v>
       </c>
       <c r="D30" t="n">
-        <v>3144</v>
+        <v>10666</v>
       </c>
       <c r="E30" t="n">
-        <v>108041</v>
+        <v>115563</v>
       </c>
       <c r="F30" t="n">
-        <v>372060</v>
+        <v>371607</v>
       </c>
       <c r="G30" t="n">
-        <v>375204</v>
+        <v>382273</v>
       </c>
       <c r="H30" t="n">
-        <v>1985</v>
+        <v>7763</v>
       </c>
       <c r="I30" t="n">
-        <v>106338</v>
+        <v>115020</v>
       </c>
       <c r="J30" t="n">
-        <v>108323</v>
+        <v>122783</v>
       </c>
       <c r="K30" t="n">
-        <v>0.6314</v>
+        <v>0.7278</v>
       </c>
       <c r="L30" t="n">
-        <v>0.2858</v>
+        <v>0.3095</v>
       </c>
       <c r="M30" t="n">
-        <v>0.2887</v>
+        <v>0.3212</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>202312</v>
+        <v>202402</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>20231201</t>
+          <t>20240201</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>3689</v>
+        <v>4092</v>
       </c>
       <c r="D31" t="n">
-        <v>53417</v>
+        <v>7236</v>
       </c>
       <c r="E31" t="n">
-        <v>104897</v>
+        <v>112133</v>
       </c>
       <c r="F31" t="n">
-        <v>318660</v>
+        <v>371597</v>
       </c>
       <c r="G31" t="n">
-        <v>372067</v>
+        <v>378833</v>
       </c>
       <c r="H31" t="n">
-        <v>39969</v>
+        <v>4888</v>
       </c>
       <c r="I31" t="n">
-        <v>121536</v>
+        <v>112247</v>
       </c>
       <c r="J31" t="n">
-        <v>161505</v>
+        <v>117135</v>
       </c>
       <c r="K31" t="n">
-        <v>0.7482</v>
+        <v>0.6755</v>
       </c>
       <c r="L31" t="n">
-        <v>0.3814</v>
+        <v>0.3021</v>
       </c>
       <c r="M31" t="n">
-        <v>0.4341</v>
+        <v>0.3092</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>202311</v>
+        <v>202401</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>20231101</t>
+          <t>20240101</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>5106</v>
+        <v>3144</v>
       </c>
       <c r="D32" t="n">
-        <v>49728</v>
+        <v>3144</v>
       </c>
       <c r="E32" t="n">
-        <v>101208</v>
+        <v>108041</v>
       </c>
       <c r="F32" t="n">
-        <v>318662</v>
+        <v>372060</v>
       </c>
       <c r="G32" t="n">
-        <v>368382</v>
+        <v>375204</v>
       </c>
       <c r="H32" t="n">
-        <v>36374</v>
+        <v>1985</v>
       </c>
       <c r="I32" t="n">
-        <v>121172</v>
+        <v>106338</v>
       </c>
       <c r="J32" t="n">
-        <v>157546</v>
+        <v>108323</v>
       </c>
       <c r="K32" t="n">
-        <v>0.7315</v>
+        <v>0.6314</v>
       </c>
       <c r="L32" t="n">
-        <v>0.3803</v>
+        <v>0.2858</v>
       </c>
       <c r="M32" t="n">
-        <v>0.4277</v>
+        <v>0.2887</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>202310</v>
+        <v>202312</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>20231001</t>
+          <t>20231201</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>4645</v>
+        <v>3689</v>
       </c>
       <c r="D33" t="n">
-        <v>44622</v>
+        <v>53417</v>
       </c>
       <c r="E33" t="n">
-        <v>96102</v>
+        <v>104897</v>
       </c>
       <c r="F33" t="n">
-        <v>318666</v>
+        <v>318660</v>
       </c>
       <c r="G33" t="n">
-        <v>363280</v>
+        <v>372067</v>
       </c>
       <c r="H33" t="n">
-        <v>32585</v>
+        <v>39969</v>
       </c>
       <c r="I33" t="n">
-        <v>120746</v>
+        <v>121536</v>
       </c>
       <c r="J33" t="n">
-        <v>153331</v>
+        <v>161505</v>
       </c>
       <c r="K33" t="n">
-        <v>0.7302</v>
+        <v>0.7482</v>
       </c>
       <c r="L33" t="n">
-        <v>0.3789</v>
+        <v>0.3814</v>
       </c>
       <c r="M33" t="n">
-        <v>0.4221</v>
+        <v>0.4341</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>202309</v>
+        <v>202311</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>20230901</t>
+          <t>20231101</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>4565</v>
+        <v>5106</v>
       </c>
       <c r="D34" t="n">
-        <v>39977</v>
+        <v>49728</v>
       </c>
       <c r="E34" t="n">
-        <v>91457</v>
+        <v>101208</v>
       </c>
       <c r="F34" t="n">
-        <v>318668</v>
+        <v>318662</v>
       </c>
       <c r="G34" t="n">
-        <v>358637</v>
+        <v>368382</v>
       </c>
       <c r="H34" t="n">
-        <v>29174</v>
+        <v>36374</v>
       </c>
       <c r="I34" t="n">
-        <v>120319</v>
+        <v>121172</v>
       </c>
       <c r="J34" t="n">
-        <v>149493</v>
+        <v>157546</v>
       </c>
       <c r="K34" t="n">
-        <v>0.7298</v>
+        <v>0.7315</v>
       </c>
       <c r="L34" t="n">
-        <v>0.3776</v>
+        <v>0.3803</v>
       </c>
       <c r="M34" t="n">
-        <v>0.4168</v>
+        <v>0.4277</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>202308</v>
+        <v>202310</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>20230801</t>
+          <t>20231001</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>4453</v>
+        <v>4645</v>
       </c>
       <c r="D35" t="n">
-        <v>35412</v>
+        <v>44622</v>
       </c>
       <c r="E35" t="n">
-        <v>86892</v>
+        <v>96102</v>
       </c>
       <c r="F35" t="n">
-        <v>318670</v>
+        <v>318666</v>
       </c>
       <c r="G35" t="n">
-        <v>354074</v>
+        <v>363280</v>
       </c>
       <c r="H35" t="n">
-        <v>25578</v>
+        <v>32585</v>
       </c>
       <c r="I35" t="n">
-        <v>119743</v>
+        <v>120746</v>
       </c>
       <c r="J35" t="n">
-        <v>145321</v>
+        <v>153331</v>
       </c>
       <c r="K35" t="n">
-        <v>0.7223000000000001</v>
+        <v>0.7302</v>
       </c>
       <c r="L35" t="n">
-        <v>0.3758</v>
+        <v>0.3789</v>
       </c>
       <c r="M35" t="n">
-        <v>0.4104</v>
+        <v>0.4221</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>202307</v>
+        <v>202309</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>20230701</t>
+          <t>20230901</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>4990</v>
+        <v>4565</v>
       </c>
       <c r="D36" t="n">
-        <v>30959</v>
+        <v>39977</v>
       </c>
       <c r="E36" t="n">
-        <v>82439</v>
+        <v>91457</v>
       </c>
       <c r="F36" t="n">
-        <v>318670</v>
+        <v>318668</v>
       </c>
       <c r="G36" t="n">
-        <v>349621</v>
+        <v>358637</v>
       </c>
       <c r="H36" t="n">
-        <v>21917</v>
+        <v>29174</v>
       </c>
       <c r="I36" t="n">
-        <v>118972</v>
+        <v>120319</v>
       </c>
       <c r="J36" t="n">
-        <v>140889</v>
+        <v>149493</v>
       </c>
       <c r="K36" t="n">
-        <v>0.7079</v>
+        <v>0.7298</v>
       </c>
       <c r="L36" t="n">
-        <v>0.3733</v>
+        <v>0.3776</v>
       </c>
       <c r="M36" t="n">
-        <v>0.403</v>
+        <v>0.4168</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>202306</v>
+        <v>202308</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>20230601</t>
+          <t>20230801</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>4676</v>
+        <v>4453</v>
       </c>
       <c r="D37" t="n">
-        <v>25969</v>
+        <v>35412</v>
       </c>
       <c r="E37" t="n">
-        <v>77449</v>
+        <v>86892</v>
       </c>
       <c r="F37" t="n">
-        <v>318673</v>
+        <v>318670</v>
       </c>
       <c r="G37" t="n">
-        <v>344634</v>
+        <v>354074</v>
       </c>
       <c r="H37" t="n">
-        <v>18330</v>
+        <v>25578</v>
       </c>
       <c r="I37" t="n">
-        <v>118009</v>
+        <v>119743</v>
       </c>
       <c r="J37" t="n">
-        <v>136339</v>
+        <v>145321</v>
       </c>
       <c r="K37" t="n">
-        <v>0.7058</v>
+        <v>0.7223000000000001</v>
       </c>
       <c r="L37" t="n">
-        <v>0.3703</v>
+        <v>0.3758</v>
       </c>
       <c r="M37" t="n">
-        <v>0.3956</v>
+        <v>0.4104</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>202305</v>
+        <v>202307</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>20230501</t>
+          <t>20230701</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>5112</v>
+        <v>4990</v>
       </c>
       <c r="D38" t="n">
-        <v>21293</v>
+        <v>30959</v>
       </c>
       <c r="E38" t="n">
-        <v>72773</v>
+        <v>82439</v>
       </c>
       <c r="F38" t="n">
-        <v>318680</v>
+        <v>318670</v>
       </c>
       <c r="G38" t="n">
-        <v>339967</v>
+        <v>349621</v>
       </c>
       <c r="H38" t="n">
-        <v>14716</v>
+        <v>21917</v>
       </c>
       <c r="I38" t="n">
-        <v>116996</v>
+        <v>118972</v>
       </c>
       <c r="J38" t="n">
-        <v>131712</v>
+        <v>140889</v>
       </c>
       <c r="K38" t="n">
-        <v>0.6911</v>
+        <v>0.7079</v>
       </c>
       <c r="L38" t="n">
-        <v>0.3671</v>
+        <v>0.3733</v>
       </c>
       <c r="M38" t="n">
-        <v>0.3874</v>
+        <v>0.403</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>202304</v>
+        <v>202306</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>20230401</t>
+          <t>20230601</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>4006</v>
+        <v>4676</v>
       </c>
       <c r="D39" t="n">
-        <v>16181</v>
+        <v>25969</v>
       </c>
       <c r="E39" t="n">
-        <v>67661</v>
+        <v>77449</v>
       </c>
       <c r="F39" t="n">
-        <v>318953</v>
+        <v>318673</v>
       </c>
       <c r="G39" t="n">
-        <v>335134</v>
+        <v>344634</v>
       </c>
       <c r="H39" t="n">
-        <v>11281</v>
+        <v>18330</v>
       </c>
       <c r="I39" t="n">
-        <v>115676</v>
+        <v>118009</v>
       </c>
       <c r="J39" t="n">
-        <v>126957</v>
+        <v>136339</v>
       </c>
       <c r="K39" t="n">
-        <v>0.6972</v>
+        <v>0.7058</v>
       </c>
       <c r="L39" t="n">
-        <v>0.3627</v>
+        <v>0.3703</v>
       </c>
       <c r="M39" t="n">
-        <v>0.3788</v>
+        <v>0.3956</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>202303</v>
+        <v>202305</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>20230301</t>
+          <t>20230501</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>4810</v>
+        <v>5112</v>
       </c>
       <c r="D40" t="n">
-        <v>12175</v>
+        <v>21293</v>
       </c>
       <c r="E40" t="n">
-        <v>63655</v>
+        <v>72773</v>
       </c>
       <c r="F40" t="n">
-        <v>318956</v>
+        <v>318680</v>
       </c>
       <c r="G40" t="n">
-        <v>331131</v>
+        <v>339967</v>
       </c>
       <c r="H40" t="n">
-        <v>8370</v>
+        <v>14716</v>
       </c>
       <c r="I40" t="n">
-        <v>113892</v>
+        <v>116996</v>
       </c>
       <c r="J40" t="n">
-        <v>122262</v>
+        <v>131712</v>
       </c>
       <c r="K40" t="n">
-        <v>0.6875</v>
+        <v>0.6911</v>
       </c>
       <c r="L40" t="n">
-        <v>0.3571</v>
+        <v>0.3671</v>
       </c>
       <c r="M40" t="n">
-        <v>0.3692</v>
+        <v>0.3874</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>202302</v>
+        <v>202304</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>20230201</t>
+          <t>20230401</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>3874</v>
+        <v>4006</v>
       </c>
       <c r="D41" t="n">
-        <v>7365</v>
+        <v>16181</v>
       </c>
       <c r="E41" t="n">
-        <v>58845</v>
+        <v>67661</v>
       </c>
       <c r="F41" t="n">
-        <v>318971</v>
+        <v>318953</v>
       </c>
       <c r="G41" t="n">
-        <v>326336</v>
+        <v>335134</v>
       </c>
       <c r="H41" t="n">
-        <v>4945</v>
+        <v>11281</v>
       </c>
       <c r="I41" t="n">
-        <v>110993</v>
+        <v>115676</v>
       </c>
       <c r="J41" t="n">
-        <v>115938</v>
+        <v>126957</v>
       </c>
       <c r="K41" t="n">
-        <v>0.6714</v>
+        <v>0.6972</v>
       </c>
       <c r="L41" t="n">
-        <v>0.348</v>
+        <v>0.3627</v>
       </c>
       <c r="M41" t="n">
-        <v>0.3553</v>
+        <v>0.3788</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>202301</v>
+        <v>202303</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>20230101</t>
+          <t>20230301</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>3491</v>
+        <v>4810</v>
       </c>
       <c r="D42" t="n">
-        <v>3491</v>
+        <v>12175</v>
       </c>
       <c r="E42" t="n">
-        <v>54971</v>
+        <v>63655</v>
       </c>
       <c r="F42" t="n">
-        <v>318972</v>
+        <v>318956</v>
       </c>
       <c r="G42" t="n">
-        <v>322463</v>
+        <v>331131</v>
       </c>
       <c r="H42" t="n">
-        <v>1975</v>
+        <v>8370</v>
       </c>
       <c r="I42" t="n">
-        <v>105502</v>
+        <v>113892</v>
       </c>
       <c r="J42" t="n">
-        <v>107477</v>
+        <v>122262</v>
       </c>
       <c r="K42" t="n">
-        <v>0.5657</v>
+        <v>0.6875</v>
       </c>
       <c r="L42" t="n">
-        <v>0.3308</v>
+        <v>0.3571</v>
       </c>
       <c r="M42" t="n">
-        <v>0.3333</v>
+        <v>0.3692</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>202212</v>
+        <v>202302</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>20221201</t>
+          <t>20230201</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>4030</v>
+        <v>3874</v>
       </c>
       <c r="D43" t="n">
-        <v>51480</v>
+        <v>7365</v>
       </c>
       <c r="E43" t="n">
-        <v>51480</v>
+        <v>58845</v>
       </c>
       <c r="F43" t="n">
-        <v>267500</v>
+        <v>318971</v>
       </c>
       <c r="G43" t="n">
-        <v>318972</v>
+        <v>326336</v>
       </c>
       <c r="H43" t="n">
-        <v>42597</v>
+        <v>4945</v>
       </c>
       <c r="I43" t="n">
-        <v>114848</v>
+        <v>110993</v>
       </c>
       <c r="J43" t="n">
-        <v>157445</v>
+        <v>115938</v>
       </c>
       <c r="K43" t="n">
-        <v>0.8274</v>
+        <v>0.6714</v>
       </c>
       <c r="L43" t="n">
-        <v>0.4293</v>
+        <v>0.348</v>
       </c>
       <c r="M43" t="n">
-        <v>0.4936</v>
+        <v>0.3553</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>202211</v>
+        <v>202301</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>20221101</t>
+          <t>20230101</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>5003</v>
+        <v>3491</v>
       </c>
       <c r="D44" t="n">
-        <v>47450</v>
+        <v>3491</v>
       </c>
       <c r="E44" t="n">
-        <v>47450</v>
+        <v>54971</v>
       </c>
       <c r="F44" t="n">
-        <v>267519</v>
+        <v>318972</v>
       </c>
       <c r="G44" t="n">
-        <v>314962</v>
+        <v>322463</v>
       </c>
       <c r="H44" t="n">
-        <v>39008</v>
+        <v>1975</v>
       </c>
       <c r="I44" t="n">
-        <v>114448</v>
+        <v>105502</v>
       </c>
       <c r="J44" t="n">
-        <v>153457</v>
+        <v>107477</v>
       </c>
       <c r="K44" t="n">
-        <v>0.8221000000000001</v>
+        <v>0.5657</v>
       </c>
       <c r="L44" t="n">
-        <v>0.4278</v>
+        <v>0.3308</v>
       </c>
       <c r="M44" t="n">
-        <v>0.4872</v>
+        <v>0.3333</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>202210</v>
+        <v>202212</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>20221001</t>
+          <t>20221201</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>4889</v>
+        <v>4030</v>
       </c>
       <c r="D45" t="n">
-        <v>42447</v>
+        <v>51480</v>
       </c>
       <c r="E45" t="n">
-        <v>42447</v>
+        <v>51480</v>
       </c>
       <c r="F45" t="n">
-        <v>267549</v>
+        <v>267500</v>
       </c>
       <c r="G45" t="n">
-        <v>309991</v>
+        <v>318972</v>
       </c>
       <c r="H45" t="n">
-        <v>34928</v>
+        <v>42597</v>
       </c>
       <c r="I45" t="n">
-        <v>114037</v>
+        <v>114848</v>
       </c>
       <c r="J45" t="n">
-        <v>148966</v>
+        <v>157445</v>
       </c>
       <c r="K45" t="n">
-        <v>0.8229</v>
+        <v>0.8274</v>
       </c>
       <c r="L45" t="n">
-        <v>0.4262</v>
+        <v>0.4293</v>
       </c>
       <c r="M45" t="n">
-        <v>0.4805</v>
+        <v>0.4936</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>202209</v>
+        <v>202211</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>20220901</t>
+          <t>20221101</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>4947</v>
+        <v>5003</v>
       </c>
       <c r="D46" t="n">
-        <v>37558</v>
+        <v>47450</v>
       </c>
       <c r="E46" t="n">
-        <v>37558</v>
+        <v>47450</v>
       </c>
       <c r="F46" t="n">
-        <v>267549</v>
+        <v>267519</v>
       </c>
       <c r="G46" t="n">
-        <v>305102</v>
+        <v>314962</v>
       </c>
       <c r="H46" t="n">
-        <v>30883</v>
+        <v>39008</v>
       </c>
       <c r="I46" t="n">
-        <v>113595</v>
+        <v>114448</v>
       </c>
       <c r="J46" t="n">
-        <v>144479</v>
+        <v>153457</v>
       </c>
       <c r="K46" t="n">
-        <v>0.8223</v>
+        <v>0.8221000000000001</v>
       </c>
       <c r="L46" t="n">
-        <v>0.4246</v>
+        <v>0.4278</v>
       </c>
       <c r="M46" t="n">
-        <v>0.4735</v>
+        <v>0.4872</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>202208</v>
+        <v>202210</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>20220801</t>
+          <t>20221001</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>4823</v>
+        <v>4889</v>
       </c>
       <c r="D47" t="n">
-        <v>32611</v>
+        <v>42447</v>
       </c>
       <c r="E47" t="n">
-        <v>32611</v>
+        <v>42447</v>
       </c>
       <c r="F47" t="n">
-        <v>267580</v>
+        <v>267549</v>
       </c>
       <c r="G47" t="n">
-        <v>300187</v>
+        <v>309991</v>
       </c>
       <c r="H47" t="n">
-        <v>26588</v>
+        <v>34928</v>
       </c>
       <c r="I47" t="n">
-        <v>113115</v>
+        <v>114037</v>
       </c>
       <c r="J47" t="n">
-        <v>139704</v>
+        <v>148966</v>
       </c>
       <c r="K47" t="n">
-        <v>0.8153</v>
+        <v>0.8229</v>
       </c>
       <c r="L47" t="n">
-        <v>0.4227</v>
+        <v>0.4262</v>
       </c>
       <c r="M47" t="n">
-        <v>0.4654</v>
+        <v>0.4805</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>202207</v>
+        <v>202209</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>20220701</t>
+          <t>20220901</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>4091</v>
+        <v>4947</v>
       </c>
       <c r="D48" t="n">
-        <v>27788</v>
+        <v>37558</v>
       </c>
       <c r="E48" t="n">
-        <v>27788</v>
+        <v>37558</v>
       </c>
       <c r="F48" t="n">
-        <v>267583</v>
+        <v>267549</v>
       </c>
       <c r="G48" t="n">
-        <v>295369</v>
+        <v>305102</v>
       </c>
       <c r="H48" t="n">
-        <v>22607</v>
+        <v>30883</v>
       </c>
       <c r="I48" t="n">
-        <v>112524</v>
+        <v>113595</v>
       </c>
       <c r="J48" t="n">
-        <v>135132</v>
+        <v>144479</v>
       </c>
       <c r="K48" t="n">
-        <v>0.8136</v>
+        <v>0.8223</v>
       </c>
       <c r="L48" t="n">
-        <v>0.4205</v>
+        <v>0.4246</v>
       </c>
       <c r="M48" t="n">
-        <v>0.4575</v>
+        <v>0.4735</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>202206</v>
+        <v>202208</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>20220601</t>
+          <t>20220801</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>4200</v>
+        <v>4823</v>
       </c>
       <c r="D49" t="n">
-        <v>23697</v>
+        <v>32611</v>
       </c>
       <c r="E49" t="n">
-        <v>23697</v>
+        <v>32611</v>
       </c>
       <c r="F49" t="n">
-        <v>267588</v>
+        <v>267580</v>
       </c>
       <c r="G49" t="n">
-        <v>291284</v>
+        <v>300187</v>
       </c>
       <c r="H49" t="n">
-        <v>19087</v>
+        <v>26588</v>
       </c>
       <c r="I49" t="n">
-        <v>111816</v>
+        <v>113115</v>
       </c>
       <c r="J49" t="n">
-        <v>130903</v>
+        <v>139704</v>
       </c>
       <c r="K49" t="n">
-        <v>0.8055</v>
+        <v>0.8153</v>
       </c>
       <c r="L49" t="n">
-        <v>0.4179</v>
+        <v>0.4227</v>
       </c>
       <c r="M49" t="n">
-        <v>0.4494</v>
+        <v>0.4654</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>202205</v>
+        <v>202207</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>20220501</t>
+          <t>20220701</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>4447</v>
+        <v>4091</v>
       </c>
       <c r="D50" t="n">
-        <v>19497</v>
+        <v>27788</v>
       </c>
       <c r="E50" t="n">
-        <v>19497</v>
+        <v>27788</v>
       </c>
       <c r="F50" t="n">
-        <v>267586</v>
+        <v>267583</v>
       </c>
       <c r="G50" t="n">
-        <v>287082</v>
+        <v>295369</v>
       </c>
       <c r="H50" t="n">
-        <v>15602</v>
+        <v>22607</v>
       </c>
       <c r="I50" t="n">
-        <v>110837</v>
+        <v>112524</v>
       </c>
       <c r="J50" t="n">
-        <v>126439</v>
+        <v>135132</v>
       </c>
       <c r="K50" t="n">
-        <v>0.8002</v>
+        <v>0.8136</v>
       </c>
       <c r="L50" t="n">
-        <v>0.4142</v>
+        <v>0.4205</v>
       </c>
       <c r="M50" t="n">
-        <v>0.4404</v>
+        <v>0.4575</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>202204</v>
+        <v>202206</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>20220401</t>
+          <t>20220601</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>3923</v>
+        <v>4200</v>
       </c>
       <c r="D51" t="n">
-        <v>15050</v>
+        <v>23697</v>
       </c>
       <c r="E51" t="n">
-        <v>15050</v>
+        <v>23697</v>
       </c>
       <c r="F51" t="n">
-        <v>267609</v>
+        <v>267588</v>
       </c>
       <c r="G51" t="n">
-        <v>282658</v>
+        <v>291284</v>
       </c>
       <c r="H51" t="n">
-        <v>11960</v>
+        <v>19087</v>
       </c>
       <c r="I51" t="n">
-        <v>109488</v>
+        <v>111816</v>
       </c>
       <c r="J51" t="n">
-        <v>121448</v>
+        <v>130903</v>
       </c>
       <c r="K51" t="n">
-        <v>0.7947</v>
+        <v>0.8055</v>
       </c>
       <c r="L51" t="n">
-        <v>0.4091</v>
+        <v>0.4179</v>
       </c>
       <c r="M51" t="n">
-        <v>0.4297</v>
+        <v>0.4494</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>202203</v>
+        <v>202205</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>20220301</t>
+          <t>20220501</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>4781</v>
+        <v>4447</v>
       </c>
       <c r="D52" t="n">
-        <v>11127</v>
+        <v>19497</v>
       </c>
       <c r="E52" t="n">
-        <v>11127</v>
+        <v>19497</v>
       </c>
       <c r="F52" t="n">
-        <v>267609</v>
+        <v>267586</v>
       </c>
       <c r="G52" t="n">
-        <v>278735</v>
+        <v>287082</v>
       </c>
       <c r="H52" t="n">
-        <v>8402</v>
+        <v>15602</v>
       </c>
       <c r="I52" t="n">
-        <v>107634</v>
+        <v>110837</v>
       </c>
       <c r="J52" t="n">
-        <v>116036</v>
+        <v>126439</v>
       </c>
       <c r="K52" t="n">
-        <v>0.7551</v>
+        <v>0.8002</v>
       </c>
       <c r="L52" t="n">
-        <v>0.4022</v>
+        <v>0.4142</v>
       </c>
       <c r="M52" t="n">
-        <v>0.4163</v>
+        <v>0.4404</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>202202</v>
+        <v>202204</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>20220201</t>
+          <t>20220401</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>3590</v>
+        <v>3923</v>
       </c>
       <c r="D53" t="n">
-        <v>6346</v>
+        <v>15050</v>
       </c>
       <c r="E53" t="n">
-        <v>6346</v>
+        <v>15050</v>
       </c>
       <c r="F53" t="n">
-        <v>267627</v>
+        <v>267609</v>
       </c>
       <c r="G53" t="n">
-        <v>273973</v>
+        <v>282658</v>
       </c>
       <c r="H53" t="n">
-        <v>4531</v>
+        <v>11960</v>
       </c>
       <c r="I53" t="n">
-        <v>104493</v>
+        <v>109488</v>
       </c>
       <c r="J53" t="n">
-        <v>109024</v>
+        <v>121448</v>
       </c>
       <c r="K53" t="n">
-        <v>0.714</v>
+        <v>0.7947</v>
       </c>
       <c r="L53" t="n">
-        <v>0.3904</v>
+        <v>0.4091</v>
       </c>
       <c r="M53" t="n">
-        <v>0.3979</v>
+        <v>0.4297</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
+        <v>202203</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>20220301</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>4781</v>
+      </c>
+      <c r="D54" t="n">
+        <v>11127</v>
+      </c>
+      <c r="E54" t="n">
+        <v>11127</v>
+      </c>
+      <c r="F54" t="n">
+        <v>267609</v>
+      </c>
+      <c r="G54" t="n">
+        <v>278735</v>
+      </c>
+      <c r="H54" t="n">
+        <v>8402</v>
+      </c>
+      <c r="I54" t="n">
+        <v>107634</v>
+      </c>
+      <c r="J54" t="n">
+        <v>116036</v>
+      </c>
+      <c r="K54" t="n">
+        <v>0.7551</v>
+      </c>
+      <c r="L54" t="n">
+        <v>0.4022</v>
+      </c>
+      <c r="M54" t="n">
+        <v>0.4163</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>202202</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>20220201</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>3590</v>
+      </c>
+      <c r="D55" t="n">
+        <v>6346</v>
+      </c>
+      <c r="E55" t="n">
+        <v>6346</v>
+      </c>
+      <c r="F55" t="n">
+        <v>267627</v>
+      </c>
+      <c r="G55" t="n">
+        <v>273973</v>
+      </c>
+      <c r="H55" t="n">
+        <v>4531</v>
+      </c>
+      <c r="I55" t="n">
+        <v>104493</v>
+      </c>
+      <c r="J55" t="n">
+        <v>109024</v>
+      </c>
+      <c r="K55" t="n">
+        <v>0.714</v>
+      </c>
+      <c r="L55" t="n">
+        <v>0.3904</v>
+      </c>
+      <c r="M55" t="n">
+        <v>0.3979</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
         <v>202201</v>
       </c>
-      <c r="B54" t="inlineStr">
+      <c r="B56" t="inlineStr">
         <is>
           <t>20220101</t>
         </is>
       </c>
-      <c r="C54" t="n">
+      <c r="C56" t="n">
         <v>2756</v>
       </c>
-      <c r="D54" t="n">
+      <c r="D56" t="n">
         <v>2756</v>
       </c>
-      <c r="E54" t="n">
+      <c r="E56" t="n">
         <v>2756</v>
       </c>
-      <c r="F54" t="n">
+      <c r="F56" t="n">
         <v>267632</v>
       </c>
-      <c r="G54" t="n">
+      <c r="G56" t="n">
         <v>270388</v>
       </c>
-      <c r="H54" t="n">
+      <c r="H56" t="n">
         <v>1628</v>
       </c>
-      <c r="I54" t="n">
+      <c r="I56" t="n">
         <v>98510</v>
       </c>
-      <c r="J54" t="n">
+      <c r="J56" t="n">
         <v>100138</v>
       </c>
-      <c r="K54" t="n">
+      <c r="K56" t="n">
         <v>0.5907</v>
       </c>
-      <c r="L54" t="n">
+      <c r="L56" t="n">
         <v>0.3681</v>
       </c>
-      <c r="M54" t="n">
+      <c r="M56" t="n">
         <v>0.3703</v>
       </c>
     </row>

--- a/main_data/evolucion_vinculacion_y_uso_adquirencia_1_a_1.xlsx
+++ b/main_data/evolucion_vinculacion_y_uso_adquirencia_1_a_1.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M56"/>
+  <dimension ref="A1:M57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -497,2366 +497,2409 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>202607</v>
+        <v>202608</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>20260701</t>
+          <t>20260801</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3812</v>
+        <v>3648</v>
       </c>
       <c r="D2" t="n">
-        <v>23778</v>
+        <v>27426</v>
       </c>
       <c r="E2" t="n">
-        <v>205509</v>
+        <v>209157</v>
       </c>
       <c r="F2" t="n">
-        <v>447611</v>
+        <v>447596</v>
       </c>
       <c r="G2" t="n">
-        <v>471385</v>
+        <v>475018</v>
       </c>
       <c r="H2" t="n">
-        <v>12093</v>
+        <v>13971</v>
       </c>
       <c r="I2" t="n">
-        <v>109345</v>
+        <v>109803</v>
       </c>
       <c r="J2" t="n">
-        <v>121439</v>
+        <v>123775</v>
       </c>
       <c r="K2" t="n">
-        <v>0.5086000000000001</v>
+        <v>0.5094</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2443</v>
+        <v>0.2453</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2576</v>
+        <v>0.2606</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>202606</v>
+        <v>202607</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>20260601</t>
+          <t>20260701</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>3107</v>
+        <v>3812</v>
       </c>
       <c r="D3" t="n">
-        <v>19966</v>
+        <v>23778</v>
       </c>
       <c r="E3" t="n">
-        <v>201697</v>
+        <v>205509</v>
       </c>
       <c r="F3" t="n">
-        <v>447619</v>
+        <v>447611</v>
       </c>
       <c r="G3" t="n">
-        <v>467583</v>
+        <v>471385</v>
       </c>
       <c r="H3" t="n">
-        <v>10280</v>
+        <v>12093</v>
       </c>
       <c r="I3" t="n">
-        <v>108755</v>
+        <v>109345</v>
       </c>
       <c r="J3" t="n">
-        <v>119036</v>
+        <v>121439</v>
       </c>
       <c r="K3" t="n">
-        <v>0.5149</v>
+        <v>0.5086000000000001</v>
       </c>
       <c r="L3" t="n">
-        <v>0.243</v>
+        <v>0.2443</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2546</v>
+        <v>0.2576</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>202605</v>
+        <v>202606</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>20260501</t>
+          <t>20260601</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>3364</v>
+        <v>3107</v>
       </c>
       <c r="D4" t="n">
-        <v>16859</v>
+        <v>19966</v>
       </c>
       <c r="E4" t="n">
-        <v>198590</v>
+        <v>201697</v>
       </c>
       <c r="F4" t="n">
-        <v>448057</v>
+        <v>447619</v>
       </c>
       <c r="G4" t="n">
-        <v>464916</v>
+        <v>467583</v>
       </c>
       <c r="H4" t="n">
-        <v>8447</v>
+        <v>10280</v>
       </c>
       <c r="I4" t="n">
-        <v>108073</v>
+        <v>108755</v>
       </c>
       <c r="J4" t="n">
-        <v>116521</v>
+        <v>119036</v>
       </c>
       <c r="K4" t="n">
-        <v>0.501</v>
+        <v>0.5149</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2412</v>
+        <v>0.243</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2506</v>
+        <v>0.2546</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>202604</v>
+        <v>202605</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>20260401</t>
+          <t>20260501</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>3739</v>
+        <v>3364</v>
       </c>
       <c r="D5" t="n">
-        <v>13495</v>
+        <v>16859</v>
       </c>
       <c r="E5" t="n">
-        <v>195226</v>
+        <v>198590</v>
       </c>
       <c r="F5" t="n">
-        <v>448056</v>
+        <v>448057</v>
       </c>
       <c r="G5" t="n">
-        <v>461551</v>
+        <v>464916</v>
       </c>
       <c r="H5" t="n">
-        <v>6523</v>
+        <v>8447</v>
       </c>
       <c r="I5" t="n">
-        <v>107059</v>
+        <v>108073</v>
       </c>
       <c r="J5" t="n">
-        <v>113583</v>
+        <v>116521</v>
       </c>
       <c r="K5" t="n">
-        <v>0.4834</v>
+        <v>0.501</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2389</v>
+        <v>0.2412</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2461</v>
+        <v>0.2506</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>202603</v>
+        <v>202604</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>20260301</t>
+          <t>20260401</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>3887</v>
+        <v>3739</v>
       </c>
       <c r="D6" t="n">
-        <v>9756</v>
+        <v>13495</v>
       </c>
       <c r="E6" t="n">
-        <v>191487</v>
+        <v>195226</v>
       </c>
       <c r="F6" t="n">
-        <v>448074</v>
+        <v>448056</v>
       </c>
       <c r="G6" t="n">
-        <v>457831</v>
+        <v>461551</v>
       </c>
       <c r="H6" t="n">
-        <v>4602</v>
+        <v>6523</v>
       </c>
       <c r="I6" t="n">
-        <v>105678</v>
+        <v>107059</v>
       </c>
       <c r="J6" t="n">
-        <v>110281</v>
+        <v>113583</v>
       </c>
       <c r="K6" t="n">
-        <v>0.4717</v>
+        <v>0.4834</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2358</v>
+        <v>0.2389</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2409</v>
+        <v>0.2461</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>202602</v>
+        <v>202603</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>20260201</t>
+          <t>20260301</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3200</v>
+        <v>3887</v>
       </c>
       <c r="D7" t="n">
-        <v>5869</v>
+        <v>9756</v>
       </c>
       <c r="E7" t="n">
-        <v>187600</v>
+        <v>191487</v>
       </c>
       <c r="F7" t="n">
-        <v>448099</v>
+        <v>448074</v>
       </c>
       <c r="G7" t="n">
-        <v>453969</v>
+        <v>457831</v>
       </c>
       <c r="H7" t="n">
-        <v>2617</v>
+        <v>4602</v>
       </c>
       <c r="I7" t="n">
-        <v>103470</v>
+        <v>105678</v>
       </c>
       <c r="J7" t="n">
-        <v>106088</v>
+        <v>110281</v>
       </c>
       <c r="K7" t="n">
-        <v>0.4459</v>
+        <v>0.4717</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2309</v>
+        <v>0.2358</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2337</v>
+        <v>0.2409</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>202601</v>
+        <v>202602</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>20260101</t>
+          <t>20260201</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2669</v>
+        <v>3200</v>
       </c>
       <c r="D8" t="n">
-        <v>2669</v>
+        <v>5869</v>
       </c>
       <c r="E8" t="n">
-        <v>184400</v>
+        <v>187600</v>
       </c>
       <c r="F8" t="n">
-        <v>448103</v>
+        <v>448099</v>
       </c>
       <c r="G8" t="n">
-        <v>450772</v>
+        <v>453969</v>
       </c>
       <c r="H8" t="n">
-        <v>1004</v>
+        <v>2617</v>
       </c>
       <c r="I8" t="n">
-        <v>98960</v>
+        <v>103470</v>
       </c>
       <c r="J8" t="n">
-        <v>99964</v>
+        <v>106088</v>
       </c>
       <c r="K8" t="n">
-        <v>0.3762</v>
+        <v>0.4459</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2208</v>
+        <v>0.2309</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2218</v>
+        <v>0.2337</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>202512</v>
+        <v>202601</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>20251201</t>
+          <t>20260101</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>3412</v>
+        <v>2669</v>
       </c>
       <c r="D9" t="n">
-        <v>38305</v>
+        <v>2669</v>
       </c>
       <c r="E9" t="n">
-        <v>181731</v>
+        <v>184400</v>
       </c>
       <c r="F9" t="n">
-        <v>409803</v>
+        <v>448103</v>
       </c>
       <c r="G9" t="n">
-        <v>448104</v>
+        <v>450772</v>
       </c>
       <c r="H9" t="n">
-        <v>24455</v>
+        <v>1004</v>
       </c>
       <c r="I9" t="n">
-        <v>113080</v>
+        <v>98960</v>
       </c>
       <c r="J9" t="n">
-        <v>137535</v>
+        <v>99964</v>
       </c>
       <c r="K9" t="n">
-        <v>0.6384</v>
+        <v>0.3762</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2759</v>
+        <v>0.2208</v>
       </c>
       <c r="M9" t="n">
-        <v>0.3069</v>
+        <v>0.2218</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>202511</v>
+        <v>202512</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>20251101</t>
+          <t>20251201</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>3284</v>
+        <v>3412</v>
       </c>
       <c r="D10" t="n">
-        <v>34893</v>
+        <v>38305</v>
       </c>
       <c r="E10" t="n">
-        <v>178319</v>
+        <v>181731</v>
       </c>
       <c r="F10" t="n">
-        <v>409832</v>
+        <v>409803</v>
       </c>
       <c r="G10" t="n">
-        <v>444725</v>
+        <v>448104</v>
       </c>
       <c r="H10" t="n">
-        <v>22119</v>
+        <v>24455</v>
       </c>
       <c r="I10" t="n">
-        <v>112697</v>
+        <v>113080</v>
       </c>
       <c r="J10" t="n">
-        <v>134816</v>
+        <v>137535</v>
       </c>
       <c r="K10" t="n">
-        <v>0.6339</v>
+        <v>0.6384</v>
       </c>
       <c r="L10" t="n">
-        <v>0.275</v>
+        <v>0.2759</v>
       </c>
       <c r="M10" t="n">
-        <v>0.3031</v>
+        <v>0.3069</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>202510</v>
+        <v>202511</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>20251001</t>
+          <t>20251101</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>3759</v>
+        <v>3284</v>
       </c>
       <c r="D11" t="n">
-        <v>31609</v>
+        <v>34893</v>
       </c>
       <c r="E11" t="n">
-        <v>175035</v>
+        <v>178319</v>
       </c>
       <c r="F11" t="n">
-        <v>409896</v>
+        <v>409832</v>
       </c>
       <c r="G11" t="n">
-        <v>441505</v>
+        <v>444725</v>
       </c>
       <c r="H11" t="n">
-        <v>20079</v>
+        <v>22119</v>
       </c>
       <c r="I11" t="n">
-        <v>112384</v>
+        <v>112697</v>
       </c>
       <c r="J11" t="n">
-        <v>132463</v>
+        <v>134816</v>
       </c>
       <c r="K11" t="n">
-        <v>0.6352</v>
+        <v>0.6339</v>
       </c>
       <c r="L11" t="n">
-        <v>0.2742</v>
+        <v>0.275</v>
       </c>
       <c r="M11" t="n">
-        <v>0.3</v>
+        <v>0.3031</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>202509</v>
+        <v>202510</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>20250901</t>
+          <t>20251001</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>3640</v>
+        <v>3759</v>
       </c>
       <c r="D12" t="n">
-        <v>27850</v>
+        <v>31609</v>
       </c>
       <c r="E12" t="n">
-        <v>171276</v>
+        <v>175035</v>
       </c>
       <c r="F12" t="n">
-        <v>409900</v>
+        <v>409896</v>
       </c>
       <c r="G12" t="n">
-        <v>437750</v>
+        <v>441505</v>
       </c>
       <c r="H12" t="n">
-        <v>17741</v>
+        <v>20079</v>
       </c>
       <c r="I12" t="n">
-        <v>111995</v>
+        <v>112384</v>
       </c>
       <c r="J12" t="n">
-        <v>129736</v>
+        <v>132463</v>
       </c>
       <c r="K12" t="n">
-        <v>0.637</v>
+        <v>0.6352</v>
       </c>
       <c r="L12" t="n">
-        <v>0.2732</v>
+        <v>0.2742</v>
       </c>
       <c r="M12" t="n">
-        <v>0.2964</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>202508</v>
+        <v>202509</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>20250801</t>
+          <t>20250901</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2970</v>
+        <v>3640</v>
       </c>
       <c r="D13" t="n">
-        <v>24210</v>
+        <v>27850</v>
       </c>
       <c r="E13" t="n">
-        <v>167636</v>
+        <v>171276</v>
       </c>
       <c r="F13" t="n">
-        <v>409903</v>
+        <v>409900</v>
       </c>
       <c r="G13" t="n">
-        <v>434113</v>
+        <v>437750</v>
       </c>
       <c r="H13" t="n">
-        <v>15543</v>
+        <v>17741</v>
       </c>
       <c r="I13" t="n">
-        <v>111498</v>
+        <v>111995</v>
       </c>
       <c r="J13" t="n">
-        <v>127041</v>
+        <v>129736</v>
       </c>
       <c r="K13" t="n">
-        <v>0.642</v>
+        <v>0.637</v>
       </c>
       <c r="L13" t="n">
-        <v>0.272</v>
+        <v>0.2732</v>
       </c>
       <c r="M13" t="n">
-        <v>0.2926</v>
+        <v>0.2964</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>202507</v>
+        <v>202508</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>20250701</t>
+          <t>20250801</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>3699</v>
+        <v>2970</v>
       </c>
       <c r="D14" t="n">
-        <v>21240</v>
+        <v>24210</v>
       </c>
       <c r="E14" t="n">
-        <v>164666</v>
+        <v>167636</v>
       </c>
       <c r="F14" t="n">
-        <v>409905</v>
+        <v>409903</v>
       </c>
       <c r="G14" t="n">
-        <v>431145</v>
+        <v>434113</v>
       </c>
       <c r="H14" t="n">
-        <v>13549</v>
+        <v>15543</v>
       </c>
       <c r="I14" t="n">
-        <v>110935</v>
+        <v>111498</v>
       </c>
       <c r="J14" t="n">
-        <v>124484</v>
+        <v>127041</v>
       </c>
       <c r="K14" t="n">
-        <v>0.6379</v>
+        <v>0.642</v>
       </c>
       <c r="L14" t="n">
-        <v>0.2706</v>
+        <v>0.272</v>
       </c>
       <c r="M14" t="n">
-        <v>0.2887</v>
+        <v>0.2926</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>202506</v>
+        <v>202507</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>20250601</t>
+          <t>20250701</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>3151</v>
+        <v>3699</v>
       </c>
       <c r="D15" t="n">
-        <v>17541</v>
+        <v>21240</v>
       </c>
       <c r="E15" t="n">
-        <v>160967</v>
+        <v>164666</v>
       </c>
       <c r="F15" t="n">
-        <v>409922</v>
+        <v>409905</v>
       </c>
       <c r="G15" t="n">
-        <v>427463</v>
+        <v>431145</v>
       </c>
       <c r="H15" t="n">
-        <v>11155</v>
+        <v>13549</v>
       </c>
       <c r="I15" t="n">
-        <v>110174</v>
+        <v>110935</v>
       </c>
       <c r="J15" t="n">
-        <v>121329</v>
+        <v>124484</v>
       </c>
       <c r="K15" t="n">
-        <v>0.6359</v>
+        <v>0.6379</v>
       </c>
       <c r="L15" t="n">
-        <v>0.2688</v>
+        <v>0.2706</v>
       </c>
       <c r="M15" t="n">
-        <v>0.2838</v>
+        <v>0.2887</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>202505</v>
+        <v>202506</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>20250501</t>
+          <t>20250601</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>3231</v>
+        <v>3151</v>
       </c>
       <c r="D16" t="n">
-        <v>14390</v>
+        <v>17541</v>
       </c>
       <c r="E16" t="n">
-        <v>157816</v>
+        <v>160967</v>
       </c>
       <c r="F16" t="n">
-        <v>409925</v>
+        <v>409922</v>
       </c>
       <c r="G16" t="n">
-        <v>424315</v>
+        <v>427463</v>
       </c>
       <c r="H16" t="n">
-        <v>9084</v>
+        <v>11155</v>
       </c>
       <c r="I16" t="n">
-        <v>109362</v>
+        <v>110174</v>
       </c>
       <c r="J16" t="n">
-        <v>118446</v>
+        <v>121329</v>
       </c>
       <c r="K16" t="n">
-        <v>0.6313</v>
+        <v>0.6359</v>
       </c>
       <c r="L16" t="n">
-        <v>0.2668</v>
+        <v>0.2688</v>
       </c>
       <c r="M16" t="n">
-        <v>0.2791</v>
+        <v>0.2838</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>202504</v>
+        <v>202505</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>20250401</t>
+          <t>20250501</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>3317</v>
+        <v>3231</v>
       </c>
       <c r="D17" t="n">
-        <v>11159</v>
+        <v>14390</v>
       </c>
       <c r="E17" t="n">
-        <v>154585</v>
+        <v>157816</v>
       </c>
       <c r="F17" t="n">
-        <v>409928</v>
+        <v>409925</v>
       </c>
       <c r="G17" t="n">
-        <v>421087</v>
+        <v>424315</v>
       </c>
       <c r="H17" t="n">
-        <v>6861</v>
+        <v>9084</v>
       </c>
       <c r="I17" t="n">
-        <v>108111</v>
+        <v>109362</v>
       </c>
       <c r="J17" t="n">
-        <v>114972</v>
+        <v>118446</v>
       </c>
       <c r="K17" t="n">
-        <v>0.6148</v>
+        <v>0.6313</v>
       </c>
       <c r="L17" t="n">
-        <v>0.2637</v>
+        <v>0.2668</v>
       </c>
       <c r="M17" t="n">
-        <v>0.273</v>
+        <v>0.2791</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>202503</v>
+        <v>202504</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>20250301</t>
+          <t>20250401</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>2887</v>
+        <v>3317</v>
       </c>
       <c r="D18" t="n">
-        <v>7842</v>
+        <v>11159</v>
       </c>
       <c r="E18" t="n">
-        <v>151268</v>
+        <v>154585</v>
       </c>
       <c r="F18" t="n">
-        <v>409953</v>
+        <v>409928</v>
       </c>
       <c r="G18" t="n">
-        <v>417795</v>
+        <v>421087</v>
       </c>
       <c r="H18" t="n">
-        <v>4674</v>
+        <v>6861</v>
       </c>
       <c r="I18" t="n">
-        <v>106615</v>
+        <v>108111</v>
       </c>
       <c r="J18" t="n">
-        <v>111289</v>
+        <v>114972</v>
       </c>
       <c r="K18" t="n">
-        <v>0.596</v>
+        <v>0.6148</v>
       </c>
       <c r="L18" t="n">
-        <v>0.2601</v>
+        <v>0.2637</v>
       </c>
       <c r="M18" t="n">
-        <v>0.2664</v>
+        <v>0.273</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>202502</v>
+        <v>202503</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>20250201</t>
+          <t>20250301</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>2691</v>
+        <v>2887</v>
       </c>
       <c r="D19" t="n">
-        <v>4955</v>
+        <v>7842</v>
       </c>
       <c r="E19" t="n">
-        <v>148381</v>
+        <v>151268</v>
       </c>
       <c r="F19" t="n">
-        <v>409938</v>
+        <v>409953</v>
       </c>
       <c r="G19" t="n">
-        <v>414893</v>
+        <v>417795</v>
       </c>
       <c r="H19" t="n">
-        <v>2828</v>
+        <v>4674</v>
       </c>
       <c r="I19" t="n">
-        <v>104133</v>
+        <v>106615</v>
       </c>
       <c r="J19" t="n">
-        <v>106961</v>
+        <v>111289</v>
       </c>
       <c r="K19" t="n">
-        <v>0.5707</v>
+        <v>0.596</v>
       </c>
       <c r="L19" t="n">
-        <v>0.254</v>
+        <v>0.2601</v>
       </c>
       <c r="M19" t="n">
-        <v>0.2578</v>
+        <v>0.2664</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>202501</v>
+        <v>202502</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>20250101</t>
+          <t>20250201</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>2264</v>
+        <v>2691</v>
       </c>
       <c r="D20" t="n">
-        <v>2264</v>
+        <v>4955</v>
       </c>
       <c r="E20" t="n">
-        <v>145690</v>
+        <v>148381</v>
       </c>
       <c r="F20" t="n">
-        <v>410060</v>
+        <v>409938</v>
       </c>
       <c r="G20" t="n">
-        <v>412324</v>
+        <v>414893</v>
       </c>
       <c r="H20" t="n">
-        <v>1159</v>
+        <v>2828</v>
       </c>
       <c r="I20" t="n">
-        <v>99434</v>
+        <v>104133</v>
       </c>
       <c r="J20" t="n">
-        <v>100593</v>
+        <v>106961</v>
       </c>
       <c r="K20" t="n">
-        <v>0.5119</v>
+        <v>0.5707</v>
       </c>
       <c r="L20" t="n">
-        <v>0.2425</v>
+        <v>0.254</v>
       </c>
       <c r="M20" t="n">
-        <v>0.244</v>
+        <v>0.2578</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>202412</v>
+        <v>202501</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>20241201</t>
+          <t>20250101</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>2910</v>
+        <v>2264</v>
       </c>
       <c r="D21" t="n">
-        <v>38529</v>
+        <v>2264</v>
       </c>
       <c r="E21" t="n">
-        <v>143426</v>
+        <v>145690</v>
       </c>
       <c r="F21" t="n">
-        <v>371557</v>
+        <v>410060</v>
       </c>
       <c r="G21" t="n">
-        <v>410078</v>
+        <v>412324</v>
       </c>
       <c r="H21" t="n">
-        <v>28109</v>
+        <v>1159</v>
       </c>
       <c r="I21" t="n">
-        <v>122366</v>
+        <v>99434</v>
       </c>
       <c r="J21" t="n">
-        <v>150475</v>
+        <v>100593</v>
       </c>
       <c r="K21" t="n">
-        <v>0.7296</v>
+        <v>0.5119</v>
       </c>
       <c r="L21" t="n">
-        <v>0.3293</v>
+        <v>0.2425</v>
       </c>
       <c r="M21" t="n">
-        <v>0.3669</v>
+        <v>0.244</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>202411</v>
+        <v>202412</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>20241101</t>
+          <t>20241201</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>2980</v>
+        <v>2910</v>
       </c>
       <c r="D22" t="n">
-        <v>35619</v>
+        <v>38529</v>
       </c>
       <c r="E22" t="n">
-        <v>140516</v>
+        <v>143426</v>
       </c>
       <c r="F22" t="n">
-        <v>371563</v>
+        <v>371557</v>
       </c>
       <c r="G22" t="n">
-        <v>407176</v>
+        <v>410078</v>
       </c>
       <c r="H22" t="n">
-        <v>25789</v>
+        <v>28109</v>
       </c>
       <c r="I22" t="n">
-        <v>122024</v>
+        <v>122366</v>
       </c>
       <c r="J22" t="n">
-        <v>147813</v>
+        <v>150475</v>
       </c>
       <c r="K22" t="n">
-        <v>0.724</v>
+        <v>0.7296</v>
       </c>
       <c r="L22" t="n">
-        <v>0.3284</v>
+        <v>0.3293</v>
       </c>
       <c r="M22" t="n">
-        <v>0.363</v>
+        <v>0.3669</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>202410</v>
+        <v>202411</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>20241001</t>
+          <t>20241101</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>3113</v>
+        <v>2980</v>
       </c>
       <c r="D23" t="n">
-        <v>32639</v>
+        <v>35619</v>
       </c>
       <c r="E23" t="n">
-        <v>137536</v>
+        <v>140516</v>
       </c>
       <c r="F23" t="n">
         <v>371563</v>
       </c>
       <c r="G23" t="n">
-        <v>404196</v>
+        <v>407176</v>
       </c>
       <c r="H23" t="n">
-        <v>23547</v>
+        <v>25789</v>
       </c>
       <c r="I23" t="n">
-        <v>121582</v>
+        <v>122024</v>
       </c>
       <c r="J23" t="n">
-        <v>145129</v>
+        <v>147813</v>
       </c>
       <c r="K23" t="n">
-        <v>0.7214</v>
+        <v>0.724</v>
       </c>
       <c r="L23" t="n">
-        <v>0.3272</v>
+        <v>0.3284</v>
       </c>
       <c r="M23" t="n">
-        <v>0.3591</v>
+        <v>0.363</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>202409</v>
+        <v>202410</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>20240901</t>
+          <t>20241001</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>3706</v>
+        <v>3113</v>
       </c>
       <c r="D24" t="n">
-        <v>29526</v>
+        <v>32639</v>
       </c>
       <c r="E24" t="n">
-        <v>134423</v>
+        <v>137536</v>
       </c>
       <c r="F24" t="n">
-        <v>371574</v>
+        <v>371563</v>
       </c>
       <c r="G24" t="n">
-        <v>401097</v>
+        <v>404196</v>
       </c>
       <c r="H24" t="n">
-        <v>21278</v>
+        <v>23547</v>
       </c>
       <c r="I24" t="n">
-        <v>121138</v>
+        <v>121582</v>
       </c>
       <c r="J24" t="n">
-        <v>142416</v>
+        <v>145129</v>
       </c>
       <c r="K24" t="n">
-        <v>0.7207</v>
+        <v>0.7214</v>
       </c>
       <c r="L24" t="n">
-        <v>0.326</v>
+        <v>0.3272</v>
       </c>
       <c r="M24" t="n">
-        <v>0.3551</v>
+        <v>0.3591</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>202408</v>
+        <v>202409</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>20240801</t>
+          <t>20240901</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>3077</v>
+        <v>3706</v>
       </c>
       <c r="D25" t="n">
-        <v>25820</v>
+        <v>29526</v>
       </c>
       <c r="E25" t="n">
-        <v>130717</v>
+        <v>134423</v>
       </c>
       <c r="F25" t="n">
-        <v>371579</v>
+        <v>371574</v>
       </c>
       <c r="G25" t="n">
-        <v>397396</v>
+        <v>401097</v>
       </c>
       <c r="H25" t="n">
-        <v>18489</v>
+        <v>21278</v>
       </c>
       <c r="I25" t="n">
-        <v>120662</v>
+        <v>121138</v>
       </c>
       <c r="J25" t="n">
-        <v>139151</v>
+        <v>142416</v>
       </c>
       <c r="K25" t="n">
-        <v>0.7161</v>
+        <v>0.7207</v>
       </c>
       <c r="L25" t="n">
-        <v>0.3247</v>
+        <v>0.326</v>
       </c>
       <c r="M25" t="n">
-        <v>0.3502</v>
+        <v>0.3551</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>202407</v>
+        <v>202408</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>20240701</t>
+          <t>20240801</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>3250</v>
+        <v>3077</v>
       </c>
       <c r="D26" t="n">
-        <v>22743</v>
+        <v>25820</v>
       </c>
       <c r="E26" t="n">
-        <v>127640</v>
+        <v>130717</v>
       </c>
       <c r="F26" t="n">
-        <v>371589</v>
+        <v>371579</v>
       </c>
       <c r="G26" t="n">
-        <v>394329</v>
+        <v>397396</v>
       </c>
       <c r="H26" t="n">
-        <v>16281</v>
+        <v>18489</v>
       </c>
       <c r="I26" t="n">
-        <v>120039</v>
+        <v>120662</v>
       </c>
       <c r="J26" t="n">
-        <v>136320</v>
+        <v>139151</v>
       </c>
       <c r="K26" t="n">
-        <v>0.7159</v>
+        <v>0.7161</v>
       </c>
       <c r="L26" t="n">
-        <v>0.323</v>
+        <v>0.3247</v>
       </c>
       <c r="M26" t="n">
-        <v>0.3457</v>
+        <v>0.3502</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>202406</v>
+        <v>202407</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>20240601</t>
+          <t>20240701</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>2683</v>
+        <v>3250</v>
       </c>
       <c r="D27" t="n">
-        <v>19493</v>
+        <v>22743</v>
       </c>
       <c r="E27" t="n">
-        <v>124390</v>
+        <v>127640</v>
       </c>
       <c r="F27" t="n">
-        <v>371581</v>
+        <v>371589</v>
       </c>
       <c r="G27" t="n">
-        <v>391072</v>
+        <v>394329</v>
       </c>
       <c r="H27" t="n">
-        <v>14112</v>
+        <v>16281</v>
       </c>
       <c r="I27" t="n">
-        <v>119205</v>
+        <v>120039</v>
       </c>
       <c r="J27" t="n">
-        <v>133317</v>
+        <v>136320</v>
       </c>
       <c r="K27" t="n">
-        <v>0.724</v>
+        <v>0.7159</v>
       </c>
       <c r="L27" t="n">
-        <v>0.3208</v>
+        <v>0.323</v>
       </c>
       <c r="M27" t="n">
-        <v>0.3409</v>
+        <v>0.3457</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>202405</v>
+        <v>202406</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>20240501</t>
+          <t>20240601</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>2946</v>
+        <v>2683</v>
       </c>
       <c r="D28" t="n">
-        <v>16810</v>
+        <v>19493</v>
       </c>
       <c r="E28" t="n">
-        <v>121707</v>
+        <v>124390</v>
       </c>
       <c r="F28" t="n">
-        <v>371587</v>
+        <v>371581</v>
       </c>
       <c r="G28" t="n">
-        <v>388397</v>
+        <v>391072</v>
       </c>
       <c r="H28" t="n">
-        <v>12260</v>
+        <v>14112</v>
       </c>
       <c r="I28" t="n">
-        <v>118299</v>
+        <v>119205</v>
       </c>
       <c r="J28" t="n">
-        <v>130559</v>
+        <v>133317</v>
       </c>
       <c r="K28" t="n">
-        <v>0.7292999999999999</v>
+        <v>0.724</v>
       </c>
       <c r="L28" t="n">
-        <v>0.3184</v>
+        <v>0.3208</v>
       </c>
       <c r="M28" t="n">
-        <v>0.3361</v>
+        <v>0.3409</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>202404</v>
+        <v>202405</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>20240401</t>
+          <t>20240501</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>3198</v>
+        <v>2946</v>
       </c>
       <c r="D29" t="n">
-        <v>13864</v>
+        <v>16810</v>
       </c>
       <c r="E29" t="n">
-        <v>118761</v>
+        <v>121707</v>
       </c>
       <c r="F29" t="n">
-        <v>371594</v>
+        <v>371587</v>
       </c>
       <c r="G29" t="n">
-        <v>385458</v>
+        <v>388397</v>
       </c>
       <c r="H29" t="n">
-        <v>9995</v>
+        <v>12260</v>
       </c>
       <c r="I29" t="n">
-        <v>116888</v>
+        <v>118299</v>
       </c>
       <c r="J29" t="n">
-        <v>126883</v>
+        <v>130559</v>
       </c>
       <c r="K29" t="n">
-        <v>0.7209</v>
+        <v>0.7292999999999999</v>
       </c>
       <c r="L29" t="n">
-        <v>0.3146</v>
+        <v>0.3184</v>
       </c>
       <c r="M29" t="n">
-        <v>0.3292</v>
+        <v>0.3361</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>202403</v>
+        <v>202404</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>20240301</t>
+          <t>20240401</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>3430</v>
+        <v>3198</v>
       </c>
       <c r="D30" t="n">
-        <v>10666</v>
+        <v>13864</v>
       </c>
       <c r="E30" t="n">
-        <v>115563</v>
+        <v>118761</v>
       </c>
       <c r="F30" t="n">
-        <v>371607</v>
+        <v>371594</v>
       </c>
       <c r="G30" t="n">
-        <v>382273</v>
+        <v>385458</v>
       </c>
       <c r="H30" t="n">
-        <v>7763</v>
+        <v>9995</v>
       </c>
       <c r="I30" t="n">
-        <v>115020</v>
+        <v>116888</v>
       </c>
       <c r="J30" t="n">
-        <v>122783</v>
+        <v>126883</v>
       </c>
       <c r="K30" t="n">
-        <v>0.7278</v>
+        <v>0.7209</v>
       </c>
       <c r="L30" t="n">
-        <v>0.3095</v>
+        <v>0.3146</v>
       </c>
       <c r="M30" t="n">
-        <v>0.3212</v>
+        <v>0.3292</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>202402</v>
+        <v>202403</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>20240201</t>
+          <t>20240301</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>4092</v>
+        <v>3430</v>
       </c>
       <c r="D31" t="n">
-        <v>7236</v>
+        <v>10666</v>
       </c>
       <c r="E31" t="n">
-        <v>112133</v>
+        <v>115563</v>
       </c>
       <c r="F31" t="n">
-        <v>371597</v>
+        <v>371607</v>
       </c>
       <c r="G31" t="n">
-        <v>378833</v>
+        <v>382273</v>
       </c>
       <c r="H31" t="n">
-        <v>4888</v>
+        <v>7763</v>
       </c>
       <c r="I31" t="n">
-        <v>112247</v>
+        <v>115020</v>
       </c>
       <c r="J31" t="n">
-        <v>117135</v>
+        <v>122783</v>
       </c>
       <c r="K31" t="n">
-        <v>0.6755</v>
+        <v>0.7278</v>
       </c>
       <c r="L31" t="n">
-        <v>0.3021</v>
+        <v>0.3095</v>
       </c>
       <c r="M31" t="n">
-        <v>0.3092</v>
+        <v>0.3212</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>202401</v>
+        <v>202402</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>20240101</t>
+          <t>20240201</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>3144</v>
+        <v>4092</v>
       </c>
       <c r="D32" t="n">
-        <v>3144</v>
+        <v>7236</v>
       </c>
       <c r="E32" t="n">
-        <v>108041</v>
+        <v>112133</v>
       </c>
       <c r="F32" t="n">
-        <v>372060</v>
+        <v>371597</v>
       </c>
       <c r="G32" t="n">
-        <v>375204</v>
+        <v>378833</v>
       </c>
       <c r="H32" t="n">
-        <v>1985</v>
+        <v>4888</v>
       </c>
       <c r="I32" t="n">
-        <v>106338</v>
+        <v>112247</v>
       </c>
       <c r="J32" t="n">
-        <v>108323</v>
+        <v>117135</v>
       </c>
       <c r="K32" t="n">
-        <v>0.6314</v>
+        <v>0.6755</v>
       </c>
       <c r="L32" t="n">
-        <v>0.2858</v>
+        <v>0.3021</v>
       </c>
       <c r="M32" t="n">
-        <v>0.2887</v>
+        <v>0.3092</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>202312</v>
+        <v>202401</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>20231201</t>
+          <t>20240101</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>3689</v>
+        <v>3144</v>
       </c>
       <c r="D33" t="n">
-        <v>53417</v>
+        <v>3144</v>
       </c>
       <c r="E33" t="n">
-        <v>104897</v>
+        <v>108041</v>
       </c>
       <c r="F33" t="n">
-        <v>318660</v>
+        <v>372060</v>
       </c>
       <c r="G33" t="n">
-        <v>372067</v>
+        <v>375204</v>
       </c>
       <c r="H33" t="n">
-        <v>39969</v>
+        <v>1985</v>
       </c>
       <c r="I33" t="n">
-        <v>121536</v>
+        <v>106338</v>
       </c>
       <c r="J33" t="n">
-        <v>161505</v>
+        <v>108323</v>
       </c>
       <c r="K33" t="n">
-        <v>0.7482</v>
+        <v>0.6314</v>
       </c>
       <c r="L33" t="n">
-        <v>0.3814</v>
+        <v>0.2858</v>
       </c>
       <c r="M33" t="n">
-        <v>0.4341</v>
+        <v>0.2887</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>202311</v>
+        <v>202312</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>20231101</t>
+          <t>20231201</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>5106</v>
+        <v>3689</v>
       </c>
       <c r="D34" t="n">
-        <v>49728</v>
+        <v>53417</v>
       </c>
       <c r="E34" t="n">
-        <v>101208</v>
+        <v>104897</v>
       </c>
       <c r="F34" t="n">
-        <v>318662</v>
+        <v>318660</v>
       </c>
       <c r="G34" t="n">
-        <v>368382</v>
+        <v>372067</v>
       </c>
       <c r="H34" t="n">
-        <v>36374</v>
+        <v>39969</v>
       </c>
       <c r="I34" t="n">
-        <v>121172</v>
+        <v>121536</v>
       </c>
       <c r="J34" t="n">
-        <v>157546</v>
+        <v>161505</v>
       </c>
       <c r="K34" t="n">
-        <v>0.7315</v>
+        <v>0.7482</v>
       </c>
       <c r="L34" t="n">
-        <v>0.3803</v>
+        <v>0.3814</v>
       </c>
       <c r="M34" t="n">
-        <v>0.4277</v>
+        <v>0.4341</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>202310</v>
+        <v>202311</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>20231001</t>
+          <t>20231101</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>4645</v>
+        <v>5106</v>
       </c>
       <c r="D35" t="n">
-        <v>44622</v>
+        <v>49728</v>
       </c>
       <c r="E35" t="n">
-        <v>96102</v>
+        <v>101208</v>
       </c>
       <c r="F35" t="n">
-        <v>318666</v>
+        <v>318662</v>
       </c>
       <c r="G35" t="n">
-        <v>363280</v>
+        <v>368382</v>
       </c>
       <c r="H35" t="n">
-        <v>32585</v>
+        <v>36374</v>
       </c>
       <c r="I35" t="n">
-        <v>120746</v>
+        <v>121172</v>
       </c>
       <c r="J35" t="n">
-        <v>153331</v>
+        <v>157546</v>
       </c>
       <c r="K35" t="n">
-        <v>0.7302</v>
+        <v>0.7315</v>
       </c>
       <c r="L35" t="n">
-        <v>0.3789</v>
+        <v>0.3803</v>
       </c>
       <c r="M35" t="n">
-        <v>0.4221</v>
+        <v>0.4277</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>202309</v>
+        <v>202310</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>20230901</t>
+          <t>20231001</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>4565</v>
+        <v>4645</v>
       </c>
       <c r="D36" t="n">
-        <v>39977</v>
+        <v>44622</v>
       </c>
       <c r="E36" t="n">
-        <v>91457</v>
+        <v>96102</v>
       </c>
       <c r="F36" t="n">
-        <v>318668</v>
+        <v>318666</v>
       </c>
       <c r="G36" t="n">
-        <v>358637</v>
+        <v>363280</v>
       </c>
       <c r="H36" t="n">
-        <v>29174</v>
+        <v>32585</v>
       </c>
       <c r="I36" t="n">
-        <v>120319</v>
+        <v>120746</v>
       </c>
       <c r="J36" t="n">
-        <v>149493</v>
+        <v>153331</v>
       </c>
       <c r="K36" t="n">
-        <v>0.7298</v>
+        <v>0.7302</v>
       </c>
       <c r="L36" t="n">
-        <v>0.3776</v>
+        <v>0.3789</v>
       </c>
       <c r="M36" t="n">
-        <v>0.4168</v>
+        <v>0.4221</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>202308</v>
+        <v>202309</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>20230801</t>
+          <t>20230901</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>4453</v>
+        <v>4565</v>
       </c>
       <c r="D37" t="n">
-        <v>35412</v>
+        <v>39977</v>
       </c>
       <c r="E37" t="n">
-        <v>86892</v>
+        <v>91457</v>
       </c>
       <c r="F37" t="n">
-        <v>318670</v>
+        <v>318668</v>
       </c>
       <c r="G37" t="n">
-        <v>354074</v>
+        <v>358637</v>
       </c>
       <c r="H37" t="n">
-        <v>25578</v>
+        <v>29174</v>
       </c>
       <c r="I37" t="n">
-        <v>119743</v>
+        <v>120319</v>
       </c>
       <c r="J37" t="n">
-        <v>145321</v>
+        <v>149493</v>
       </c>
       <c r="K37" t="n">
-        <v>0.7223000000000001</v>
+        <v>0.7298</v>
       </c>
       <c r="L37" t="n">
-        <v>0.3758</v>
+        <v>0.3776</v>
       </c>
       <c r="M37" t="n">
-        <v>0.4104</v>
+        <v>0.4168</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>202307</v>
+        <v>202308</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>20230701</t>
+          <t>20230801</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>4990</v>
+        <v>4453</v>
       </c>
       <c r="D38" t="n">
-        <v>30959</v>
+        <v>35412</v>
       </c>
       <c r="E38" t="n">
-        <v>82439</v>
+        <v>86892</v>
       </c>
       <c r="F38" t="n">
         <v>318670</v>
       </c>
       <c r="G38" t="n">
-        <v>349621</v>
+        <v>354074</v>
       </c>
       <c r="H38" t="n">
-        <v>21917</v>
+        <v>25578</v>
       </c>
       <c r="I38" t="n">
-        <v>118972</v>
+        <v>119743</v>
       </c>
       <c r="J38" t="n">
-        <v>140889</v>
+        <v>145321</v>
       </c>
       <c r="K38" t="n">
-        <v>0.7079</v>
+        <v>0.7223000000000001</v>
       </c>
       <c r="L38" t="n">
-        <v>0.3733</v>
+        <v>0.3758</v>
       </c>
       <c r="M38" t="n">
-        <v>0.403</v>
+        <v>0.4104</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>202306</v>
+        <v>202307</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>20230601</t>
+          <t>20230701</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>4676</v>
+        <v>4990</v>
       </c>
       <c r="D39" t="n">
-        <v>25969</v>
+        <v>30959</v>
       </c>
       <c r="E39" t="n">
-        <v>77449</v>
+        <v>82439</v>
       </c>
       <c r="F39" t="n">
-        <v>318673</v>
+        <v>318670</v>
       </c>
       <c r="G39" t="n">
-        <v>344634</v>
+        <v>349621</v>
       </c>
       <c r="H39" t="n">
-        <v>18330</v>
+        <v>21917</v>
       </c>
       <c r="I39" t="n">
-        <v>118009</v>
+        <v>118972</v>
       </c>
       <c r="J39" t="n">
-        <v>136339</v>
+        <v>140889</v>
       </c>
       <c r="K39" t="n">
-        <v>0.7058</v>
+        <v>0.7079</v>
       </c>
       <c r="L39" t="n">
-        <v>0.3703</v>
+        <v>0.3733</v>
       </c>
       <c r="M39" t="n">
-        <v>0.3956</v>
+        <v>0.403</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>202305</v>
+        <v>202306</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>20230501</t>
+          <t>20230601</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>5112</v>
+        <v>4676</v>
       </c>
       <c r="D40" t="n">
-        <v>21293</v>
+        <v>25969</v>
       </c>
       <c r="E40" t="n">
-        <v>72773</v>
+        <v>77449</v>
       </c>
       <c r="F40" t="n">
-        <v>318680</v>
+        <v>318673</v>
       </c>
       <c r="G40" t="n">
-        <v>339967</v>
+        <v>344634</v>
       </c>
       <c r="H40" t="n">
-        <v>14716</v>
+        <v>18330</v>
       </c>
       <c r="I40" t="n">
-        <v>116996</v>
+        <v>118009</v>
       </c>
       <c r="J40" t="n">
-        <v>131712</v>
+        <v>136339</v>
       </c>
       <c r="K40" t="n">
-        <v>0.6911</v>
+        <v>0.7058</v>
       </c>
       <c r="L40" t="n">
-        <v>0.3671</v>
+        <v>0.3703</v>
       </c>
       <c r="M40" t="n">
-        <v>0.3874</v>
+        <v>0.3956</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>202304</v>
+        <v>202305</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>20230401</t>
+          <t>20230501</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>4006</v>
+        <v>5112</v>
       </c>
       <c r="D41" t="n">
-        <v>16181</v>
+        <v>21293</v>
       </c>
       <c r="E41" t="n">
-        <v>67661</v>
+        <v>72773</v>
       </c>
       <c r="F41" t="n">
-        <v>318953</v>
+        <v>318680</v>
       </c>
       <c r="G41" t="n">
-        <v>335134</v>
+        <v>339967</v>
       </c>
       <c r="H41" t="n">
-        <v>11281</v>
+        <v>14716</v>
       </c>
       <c r="I41" t="n">
-        <v>115676</v>
+        <v>116996</v>
       </c>
       <c r="J41" t="n">
-        <v>126957</v>
+        <v>131712</v>
       </c>
       <c r="K41" t="n">
-        <v>0.6972</v>
+        <v>0.6911</v>
       </c>
       <c r="L41" t="n">
-        <v>0.3627</v>
+        <v>0.3671</v>
       </c>
       <c r="M41" t="n">
-        <v>0.3788</v>
+        <v>0.3874</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>202303</v>
+        <v>202304</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>20230301</t>
+          <t>20230401</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>4810</v>
+        <v>4006</v>
       </c>
       <c r="D42" t="n">
-        <v>12175</v>
+        <v>16181</v>
       </c>
       <c r="E42" t="n">
-        <v>63655</v>
+        <v>67661</v>
       </c>
       <c r="F42" t="n">
-        <v>318956</v>
+        <v>318953</v>
       </c>
       <c r="G42" t="n">
-        <v>331131</v>
+        <v>335134</v>
       </c>
       <c r="H42" t="n">
-        <v>8370</v>
+        <v>11281</v>
       </c>
       <c r="I42" t="n">
-        <v>113892</v>
+        <v>115676</v>
       </c>
       <c r="J42" t="n">
-        <v>122262</v>
+        <v>126957</v>
       </c>
       <c r="K42" t="n">
-        <v>0.6875</v>
+        <v>0.6972</v>
       </c>
       <c r="L42" t="n">
-        <v>0.3571</v>
+        <v>0.3627</v>
       </c>
       <c r="M42" t="n">
-        <v>0.3692</v>
+        <v>0.3788</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>202302</v>
+        <v>202303</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>20230201</t>
+          <t>20230301</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>3874</v>
+        <v>4810</v>
       </c>
       <c r="D43" t="n">
-        <v>7365</v>
+        <v>12175</v>
       </c>
       <c r="E43" t="n">
-        <v>58845</v>
+        <v>63655</v>
       </c>
       <c r="F43" t="n">
-        <v>318971</v>
+        <v>318956</v>
       </c>
       <c r="G43" t="n">
-        <v>326336</v>
+        <v>331131</v>
       </c>
       <c r="H43" t="n">
-        <v>4945</v>
+        <v>8370</v>
       </c>
       <c r="I43" t="n">
-        <v>110993</v>
+        <v>113892</v>
       </c>
       <c r="J43" t="n">
-        <v>115938</v>
+        <v>122262</v>
       </c>
       <c r="K43" t="n">
-        <v>0.6714</v>
+        <v>0.6875</v>
       </c>
       <c r="L43" t="n">
-        <v>0.348</v>
+        <v>0.3571</v>
       </c>
       <c r="M43" t="n">
-        <v>0.3553</v>
+        <v>0.3692</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>202301</v>
+        <v>202302</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>20230101</t>
+          <t>20230201</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>3491</v>
+        <v>3874</v>
       </c>
       <c r="D44" t="n">
-        <v>3491</v>
+        <v>7365</v>
       </c>
       <c r="E44" t="n">
-        <v>54971</v>
+        <v>58845</v>
       </c>
       <c r="F44" t="n">
-        <v>318972</v>
+        <v>318971</v>
       </c>
       <c r="G44" t="n">
-        <v>322463</v>
+        <v>326336</v>
       </c>
       <c r="H44" t="n">
-        <v>1975</v>
+        <v>4945</v>
       </c>
       <c r="I44" t="n">
-        <v>105502</v>
+        <v>110993</v>
       </c>
       <c r="J44" t="n">
-        <v>107477</v>
+        <v>115938</v>
       </c>
       <c r="K44" t="n">
-        <v>0.5657</v>
+        <v>0.6714</v>
       </c>
       <c r="L44" t="n">
-        <v>0.3308</v>
+        <v>0.348</v>
       </c>
       <c r="M44" t="n">
-        <v>0.3333</v>
+        <v>0.3553</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>202212</v>
+        <v>202301</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>20221201</t>
+          <t>20230101</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>4030</v>
+        <v>3491</v>
       </c>
       <c r="D45" t="n">
-        <v>51480</v>
+        <v>3491</v>
       </c>
       <c r="E45" t="n">
-        <v>51480</v>
+        <v>54971</v>
       </c>
       <c r="F45" t="n">
-        <v>267500</v>
+        <v>318972</v>
       </c>
       <c r="G45" t="n">
-        <v>318972</v>
+        <v>322463</v>
       </c>
       <c r="H45" t="n">
-        <v>42597</v>
+        <v>1975</v>
       </c>
       <c r="I45" t="n">
-        <v>114848</v>
+        <v>105502</v>
       </c>
       <c r="J45" t="n">
-        <v>157445</v>
+        <v>107477</v>
       </c>
       <c r="K45" t="n">
-        <v>0.8274</v>
+        <v>0.5657</v>
       </c>
       <c r="L45" t="n">
-        <v>0.4293</v>
+        <v>0.3308</v>
       </c>
       <c r="M45" t="n">
-        <v>0.4936</v>
+        <v>0.3333</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>202211</v>
+        <v>202212</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>20221101</t>
+          <t>20221201</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>5003</v>
+        <v>4030</v>
       </c>
       <c r="D46" t="n">
-        <v>47450</v>
+        <v>51480</v>
       </c>
       <c r="E46" t="n">
-        <v>47450</v>
+        <v>51480</v>
       </c>
       <c r="F46" t="n">
-        <v>267519</v>
+        <v>267500</v>
       </c>
       <c r="G46" t="n">
-        <v>314962</v>
+        <v>318972</v>
       </c>
       <c r="H46" t="n">
-        <v>39008</v>
+        <v>42597</v>
       </c>
       <c r="I46" t="n">
-        <v>114448</v>
+        <v>114848</v>
       </c>
       <c r="J46" t="n">
-        <v>153457</v>
+        <v>157445</v>
       </c>
       <c r="K46" t="n">
-        <v>0.8221000000000001</v>
+        <v>0.8274</v>
       </c>
       <c r="L46" t="n">
-        <v>0.4278</v>
+        <v>0.4293</v>
       </c>
       <c r="M46" t="n">
-        <v>0.4872</v>
+        <v>0.4936</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>202210</v>
+        <v>202211</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>20221001</t>
+          <t>20221101</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>4889</v>
+        <v>5003</v>
       </c>
       <c r="D47" t="n">
-        <v>42447</v>
+        <v>47450</v>
       </c>
       <c r="E47" t="n">
-        <v>42447</v>
+        <v>47450</v>
       </c>
       <c r="F47" t="n">
-        <v>267549</v>
+        <v>267519</v>
       </c>
       <c r="G47" t="n">
-        <v>309991</v>
+        <v>314962</v>
       </c>
       <c r="H47" t="n">
-        <v>34928</v>
+        <v>39008</v>
       </c>
       <c r="I47" t="n">
-        <v>114037</v>
+        <v>114448</v>
       </c>
       <c r="J47" t="n">
-        <v>148966</v>
+        <v>153457</v>
       </c>
       <c r="K47" t="n">
-        <v>0.8229</v>
+        <v>0.8221000000000001</v>
       </c>
       <c r="L47" t="n">
-        <v>0.4262</v>
+        <v>0.4278</v>
       </c>
       <c r="M47" t="n">
-        <v>0.4805</v>
+        <v>0.4872</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>202209</v>
+        <v>202210</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>20220901</t>
+          <t>20221001</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>4947</v>
+        <v>4889</v>
       </c>
       <c r="D48" t="n">
-        <v>37558</v>
+        <v>42447</v>
       </c>
       <c r="E48" t="n">
-        <v>37558</v>
+        <v>42447</v>
       </c>
       <c r="F48" t="n">
         <v>267549</v>
       </c>
       <c r="G48" t="n">
-        <v>305102</v>
+        <v>309991</v>
       </c>
       <c r="H48" t="n">
-        <v>30883</v>
+        <v>34928</v>
       </c>
       <c r="I48" t="n">
-        <v>113595</v>
+        <v>114037</v>
       </c>
       <c r="J48" t="n">
-        <v>144479</v>
+        <v>148966</v>
       </c>
       <c r="K48" t="n">
-        <v>0.8223</v>
+        <v>0.8229</v>
       </c>
       <c r="L48" t="n">
-        <v>0.4246</v>
+        <v>0.4262</v>
       </c>
       <c r="M48" t="n">
-        <v>0.4735</v>
+        <v>0.4805</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>202208</v>
+        <v>202209</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>20220801</t>
+          <t>20220901</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>4823</v>
+        <v>4947</v>
       </c>
       <c r="D49" t="n">
-        <v>32611</v>
+        <v>37558</v>
       </c>
       <c r="E49" t="n">
-        <v>32611</v>
+        <v>37558</v>
       </c>
       <c r="F49" t="n">
-        <v>267580</v>
+        <v>267549</v>
       </c>
       <c r="G49" t="n">
-        <v>300187</v>
+        <v>305102</v>
       </c>
       <c r="H49" t="n">
-        <v>26588</v>
+        <v>30883</v>
       </c>
       <c r="I49" t="n">
-        <v>113115</v>
+        <v>113595</v>
       </c>
       <c r="J49" t="n">
-        <v>139704</v>
+        <v>144479</v>
       </c>
       <c r="K49" t="n">
-        <v>0.8153</v>
+        <v>0.8223</v>
       </c>
       <c r="L49" t="n">
-        <v>0.4227</v>
+        <v>0.4246</v>
       </c>
       <c r="M49" t="n">
-        <v>0.4654</v>
+        <v>0.4735</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>202207</v>
+        <v>202208</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>20220701</t>
+          <t>20220801</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>4091</v>
+        <v>4823</v>
       </c>
       <c r="D50" t="n">
-        <v>27788</v>
+        <v>32611</v>
       </c>
       <c r="E50" t="n">
-        <v>27788</v>
+        <v>32611</v>
       </c>
       <c r="F50" t="n">
-        <v>267583</v>
+        <v>267580</v>
       </c>
       <c r="G50" t="n">
-        <v>295369</v>
+        <v>300187</v>
       </c>
       <c r="H50" t="n">
-        <v>22607</v>
+        <v>26588</v>
       </c>
       <c r="I50" t="n">
-        <v>112524</v>
+        <v>113115</v>
       </c>
       <c r="J50" t="n">
-        <v>135132</v>
+        <v>139704</v>
       </c>
       <c r="K50" t="n">
-        <v>0.8136</v>
+        <v>0.8153</v>
       </c>
       <c r="L50" t="n">
-        <v>0.4205</v>
+        <v>0.4227</v>
       </c>
       <c r="M50" t="n">
-        <v>0.4575</v>
+        <v>0.4654</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>202206</v>
+        <v>202207</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>20220601</t>
+          <t>20220701</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>4200</v>
+        <v>4091</v>
       </c>
       <c r="D51" t="n">
-        <v>23697</v>
+        <v>27788</v>
       </c>
       <c r="E51" t="n">
-        <v>23697</v>
+        <v>27788</v>
       </c>
       <c r="F51" t="n">
-        <v>267588</v>
+        <v>267583</v>
       </c>
       <c r="G51" t="n">
-        <v>291284</v>
+        <v>295369</v>
       </c>
       <c r="H51" t="n">
-        <v>19087</v>
+        <v>22607</v>
       </c>
       <c r="I51" t="n">
-        <v>111816</v>
+        <v>112524</v>
       </c>
       <c r="J51" t="n">
-        <v>130903</v>
+        <v>135132</v>
       </c>
       <c r="K51" t="n">
-        <v>0.8055</v>
+        <v>0.8136</v>
       </c>
       <c r="L51" t="n">
-        <v>0.4179</v>
+        <v>0.4205</v>
       </c>
       <c r="M51" t="n">
-        <v>0.4494</v>
+        <v>0.4575</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>202205</v>
+        <v>202206</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>20220501</t>
+          <t>20220601</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>4447</v>
+        <v>4200</v>
       </c>
       <c r="D52" t="n">
-        <v>19497</v>
+        <v>23697</v>
       </c>
       <c r="E52" t="n">
-        <v>19497</v>
+        <v>23697</v>
       </c>
       <c r="F52" t="n">
-        <v>267586</v>
+        <v>267588</v>
       </c>
       <c r="G52" t="n">
-        <v>287082</v>
+        <v>291284</v>
       </c>
       <c r="H52" t="n">
-        <v>15602</v>
+        <v>19087</v>
       </c>
       <c r="I52" t="n">
-        <v>110837</v>
+        <v>111816</v>
       </c>
       <c r="J52" t="n">
-        <v>126439</v>
+        <v>130903</v>
       </c>
       <c r="K52" t="n">
-        <v>0.8002</v>
+        <v>0.8055</v>
       </c>
       <c r="L52" t="n">
-        <v>0.4142</v>
+        <v>0.4179</v>
       </c>
       <c r="M52" t="n">
-        <v>0.4404</v>
+        <v>0.4494</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>202204</v>
+        <v>202205</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>20220401</t>
+          <t>20220501</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>3923</v>
+        <v>4447</v>
       </c>
       <c r="D53" t="n">
-        <v>15050</v>
+        <v>19497</v>
       </c>
       <c r="E53" t="n">
-        <v>15050</v>
+        <v>19497</v>
       </c>
       <c r="F53" t="n">
-        <v>267609</v>
+        <v>267586</v>
       </c>
       <c r="G53" t="n">
-        <v>282658</v>
+        <v>287082</v>
       </c>
       <c r="H53" t="n">
-        <v>11960</v>
+        <v>15602</v>
       </c>
       <c r="I53" t="n">
-        <v>109488</v>
+        <v>110837</v>
       </c>
       <c r="J53" t="n">
-        <v>121448</v>
+        <v>126439</v>
       </c>
       <c r="K53" t="n">
-        <v>0.7947</v>
+        <v>0.8002</v>
       </c>
       <c r="L53" t="n">
-        <v>0.4091</v>
+        <v>0.4142</v>
       </c>
       <c r="M53" t="n">
-        <v>0.4297</v>
+        <v>0.4404</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>202203</v>
+        <v>202204</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>20220301</t>
+          <t>20220401</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>4781</v>
+        <v>3923</v>
       </c>
       <c r="D54" t="n">
-        <v>11127</v>
+        <v>15050</v>
       </c>
       <c r="E54" t="n">
-        <v>11127</v>
+        <v>15050</v>
       </c>
       <c r="F54" t="n">
         <v>267609</v>
       </c>
       <c r="G54" t="n">
-        <v>278735</v>
+        <v>282658</v>
       </c>
       <c r="H54" t="n">
-        <v>8402</v>
+        <v>11960</v>
       </c>
       <c r="I54" t="n">
-        <v>107634</v>
+        <v>109488</v>
       </c>
       <c r="J54" t="n">
-        <v>116036</v>
+        <v>121448</v>
       </c>
       <c r="K54" t="n">
-        <v>0.7551</v>
+        <v>0.7947</v>
       </c>
       <c r="L54" t="n">
-        <v>0.4022</v>
+        <v>0.4091</v>
       </c>
       <c r="M54" t="n">
-        <v>0.4163</v>
+        <v>0.4297</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>202202</v>
+        <v>202203</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>20220201</t>
+          <t>20220301</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>3590</v>
+        <v>4781</v>
       </c>
       <c r="D55" t="n">
-        <v>6346</v>
+        <v>11127</v>
       </c>
       <c r="E55" t="n">
-        <v>6346</v>
+        <v>11127</v>
       </c>
       <c r="F55" t="n">
-        <v>267627</v>
+        <v>267609</v>
       </c>
       <c r="G55" t="n">
-        <v>273973</v>
+        <v>278735</v>
       </c>
       <c r="H55" t="n">
-        <v>4531</v>
+        <v>8402</v>
       </c>
       <c r="I55" t="n">
-        <v>104493</v>
+        <v>107634</v>
       </c>
       <c r="J55" t="n">
-        <v>109024</v>
+        <v>116036</v>
       </c>
       <c r="K55" t="n">
-        <v>0.714</v>
+        <v>0.7551</v>
       </c>
       <c r="L55" t="n">
-        <v>0.3904</v>
+        <v>0.4022</v>
       </c>
       <c r="M55" t="n">
-        <v>0.3979</v>
+        <v>0.4163</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
+        <v>202202</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>20220201</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>3590</v>
+      </c>
+      <c r="D56" t="n">
+        <v>6346</v>
+      </c>
+      <c r="E56" t="n">
+        <v>6346</v>
+      </c>
+      <c r="F56" t="n">
+        <v>267627</v>
+      </c>
+      <c r="G56" t="n">
+        <v>273973</v>
+      </c>
+      <c r="H56" t="n">
+        <v>4531</v>
+      </c>
+      <c r="I56" t="n">
+        <v>104493</v>
+      </c>
+      <c r="J56" t="n">
+        <v>109024</v>
+      </c>
+      <c r="K56" t="n">
+        <v>0.714</v>
+      </c>
+      <c r="L56" t="n">
+        <v>0.3904</v>
+      </c>
+      <c r="M56" t="n">
+        <v>0.3979</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
         <v>202201</v>
       </c>
-      <c r="B56" t="inlineStr">
+      <c r="B57" t="inlineStr">
         <is>
           <t>20220101</t>
         </is>
       </c>
-      <c r="C56" t="n">
+      <c r="C57" t="n">
         <v>2756</v>
       </c>
-      <c r="D56" t="n">
+      <c r="D57" t="n">
         <v>2756</v>
       </c>
-      <c r="E56" t="n">
+      <c r="E57" t="n">
         <v>2756</v>
       </c>
-      <c r="F56" t="n">
+      <c r="F57" t="n">
         <v>267632</v>
       </c>
-      <c r="G56" t="n">
+      <c r="G57" t="n">
         <v>270388</v>
       </c>
-      <c r="H56" t="n">
+      <c r="H57" t="n">
         <v>1628</v>
       </c>
-      <c r="I56" t="n">
+      <c r="I57" t="n">
         <v>98510</v>
       </c>
-      <c r="J56" t="n">
+      <c r="J57" t="n">
         <v>100138</v>
       </c>
-      <c r="K56" t="n">
+      <c r="K57" t="n">
         <v>0.5907</v>
       </c>
-      <c r="L56" t="n">
+      <c r="L57" t="n">
         <v>0.3681</v>
       </c>
-      <c r="M56" t="n">
+      <c r="M57" t="n">
         <v>0.3703</v>
       </c>
     </row>
